--- a/data-raw/preferenties/Preferentietabel 9 chloride in oppervlaktewater.xlsx
+++ b/data-raw/preferenties/Preferentietabel 9 chloride in oppervlaktewater.xlsx
@@ -1,22 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/24f2756d9d8bedf6/Documents/ZZP/Projecten - lopend/Fase 2 - W^0W/Achtergronddocument/Preferentietabellen achtergrondrapport/Oppervlaktewater/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R\waterplanten\data-raw\preferenties\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="66" documentId="13_ncr:9_{4CD17FCC-09F0-4185-A165-B30DA4DBB570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C4FE6F4-6F43-47D3-B7E2-107EC230257D}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{822DEC36-EC22-4C45-AA9F-2C0805121CE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{90B234F7-A996-4BF6-897D-F71D9109DF7D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{90B234F7-A996-4BF6-897D-F71D9109DF7D}"/>
   </bookViews>
   <sheets>
     <sheet name="Eind_tabel_Cl._W_umol.l2025-01-" sheetId="1" r:id="rId1"/>
+    <sheet name="ORIG" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Eind_tabel_Cl._W_umol.l2025-01-'!$A$8:$S$120</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Eind_tabel_Cl._W_umol.l2025-01-'!$A$6:$S$118</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">ORIG!$A$8:$S$120</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="269">
   <si>
     <t>ind = indicatiegewicht, gemod. chi = gemodificeerde chi-waarde; gewogen gemid. = gewogen gemiddelde; opt =  optimum; 90-quantiel = 90 kwantiel percentage; voor uitleg, zie Van Geest et al. (2025)</t>
   </si>
@@ -1459,24 +1461,24 @@
     <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
     <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
     <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Berekening" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Controlecel" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Gekoppelde cel" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Goed" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Invoer" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Kop 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Kop 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Kop 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Kop 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Neutraal" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="Notitie" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Ongeldig" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
+    <cellStyle name="Titel" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Totaal" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Uitvoer" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Verklarende tekst" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Waarschuwingstekst" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1492,7 +1494,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Kantoorthema">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1808,26 +1810,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE499DF5-0C89-4A3F-ACDF-66AC73FB500F}">
-  <dimension ref="A1:S124"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:S122"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.86328125" customWidth="1"/>
-    <col min="2" max="2" width="31.265625" customWidth="1"/>
-    <col min="4" max="14" width="12.265625" customWidth="1"/>
+    <col min="1" max="1" width="29.85546875" customWidth="1"/>
+    <col min="2" max="2" width="31.28515625" customWidth="1"/>
+    <col min="4" max="14" width="12.28515625" customWidth="1"/>
     <col min="15" max="19" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>1</v>
       </c>
@@ -1872,7 +1874,6998 @@
       <c r="R4" s="9"/>
       <c r="S4" s="9"/>
     </row>
-    <row r="5" spans="1:19" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:19" s="1" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="K5" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="L5" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M5" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="O5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="R5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="S5" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="1">
+        <v>10</v>
+      </c>
+      <c r="D6" s="1">
+        <v>100</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1">
+        <v>0</v>
+      </c>
+      <c r="L6" s="1">
+        <v>0</v>
+      </c>
+      <c r="M6" s="1">
+        <v>0</v>
+      </c>
+      <c r="N6" s="1">
+        <v>0</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P6" s="1">
+        <v>352</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>310</v>
+      </c>
+      <c r="R6" s="1">
+        <v>10</v>
+      </c>
+      <c r="S6" s="1">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="1">
+        <v>19</v>
+      </c>
+      <c r="D7" s="1">
+        <v>100</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0</v>
+      </c>
+      <c r="J7" s="1">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1">
+        <v>0</v>
+      </c>
+      <c r="L7" s="1">
+        <v>0</v>
+      </c>
+      <c r="M7" s="1">
+        <v>0</v>
+      </c>
+      <c r="N7" s="1">
+        <v>0</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P7" s="1">
+        <v>380</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>352</v>
+      </c>
+      <c r="R7" s="1">
+        <v>10</v>
+      </c>
+      <c r="S7" s="1">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="1">
+        <v>26</v>
+      </c>
+      <c r="D8" s="1">
+        <v>100</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0</v>
+      </c>
+      <c r="I8" s="1">
+        <v>0</v>
+      </c>
+      <c r="J8" s="1">
+        <v>0</v>
+      </c>
+      <c r="K8" s="1">
+        <v>0</v>
+      </c>
+      <c r="L8" s="1">
+        <v>0</v>
+      </c>
+      <c r="M8" s="1">
+        <v>0</v>
+      </c>
+      <c r="N8" s="1">
+        <v>0</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P8" s="1">
+        <v>402</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>423</v>
+      </c>
+      <c r="R8" s="1">
+        <v>10</v>
+      </c>
+      <c r="S8" s="1">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="1">
+        <v>16</v>
+      </c>
+      <c r="D9" s="1">
+        <v>100</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0</v>
+      </c>
+      <c r="I9" s="1">
+        <v>0</v>
+      </c>
+      <c r="J9" s="1">
+        <v>0</v>
+      </c>
+      <c r="K9" s="1">
+        <v>0</v>
+      </c>
+      <c r="L9" s="1">
+        <v>0</v>
+      </c>
+      <c r="M9" s="1">
+        <v>0</v>
+      </c>
+      <c r="N9" s="1">
+        <v>0</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P9" s="1">
+        <v>413</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>390</v>
+      </c>
+      <c r="R9" s="1">
+        <v>10</v>
+      </c>
+      <c r="S9" s="1">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="1">
+        <v>14</v>
+      </c>
+      <c r="D10" s="1">
+        <v>100</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0</v>
+      </c>
+      <c r="I10" s="1">
+        <v>0</v>
+      </c>
+      <c r="J10" s="1">
+        <v>0</v>
+      </c>
+      <c r="K10" s="1">
+        <v>0</v>
+      </c>
+      <c r="L10" s="1">
+        <v>0</v>
+      </c>
+      <c r="M10" s="1">
+        <v>0</v>
+      </c>
+      <c r="N10" s="1">
+        <v>0</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P10" s="1">
+        <v>507</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>498</v>
+      </c>
+      <c r="R10" s="1">
+        <v>10</v>
+      </c>
+      <c r="S10" s="1">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="1">
+        <v>38</v>
+      </c>
+      <c r="D11" s="1">
+        <v>86</v>
+      </c>
+      <c r="E11" s="1">
+        <v>14</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1">
+        <v>0</v>
+      </c>
+      <c r="I11" s="1">
+        <v>0</v>
+      </c>
+      <c r="J11" s="1">
+        <v>0</v>
+      </c>
+      <c r="K11" s="1">
+        <v>0</v>
+      </c>
+      <c r="L11" s="1">
+        <v>0</v>
+      </c>
+      <c r="M11" s="1">
+        <v>0</v>
+      </c>
+      <c r="N11" s="1">
+        <v>0</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P11" s="1">
+        <v>619</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>502</v>
+      </c>
+      <c r="R11" s="1">
+        <v>7.31</v>
+      </c>
+      <c r="S11" s="1">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="1">
+        <v>31</v>
+      </c>
+      <c r="D12" s="1">
+        <v>91</v>
+      </c>
+      <c r="E12" s="1">
+        <v>9</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0</v>
+      </c>
+      <c r="I12" s="1">
+        <v>0</v>
+      </c>
+      <c r="J12" s="1">
+        <v>0</v>
+      </c>
+      <c r="K12" s="1">
+        <v>0</v>
+      </c>
+      <c r="L12" s="1">
+        <v>0</v>
+      </c>
+      <c r="M12" s="1">
+        <v>0</v>
+      </c>
+      <c r="N12" s="1">
+        <v>0</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P12" s="1">
+        <v>628</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>621</v>
+      </c>
+      <c r="R12" s="1">
+        <v>8.18</v>
+      </c>
+      <c r="S12" s="1">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="1">
+        <v>5</v>
+      </c>
+      <c r="D13" s="1">
+        <v>100</v>
+      </c>
+      <c r="E13" s="1">
+        <v>0</v>
+      </c>
+      <c r="F13" s="1">
+        <v>0</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
+        <v>0</v>
+      </c>
+      <c r="I13" s="1">
+        <v>0</v>
+      </c>
+      <c r="J13" s="1">
+        <v>0</v>
+      </c>
+      <c r="K13" s="1">
+        <v>0</v>
+      </c>
+      <c r="L13" s="1">
+        <v>0</v>
+      </c>
+      <c r="M13" s="1">
+        <v>0</v>
+      </c>
+      <c r="N13" s="1">
+        <v>0</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P13" s="1">
+        <v>659</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>712</v>
+      </c>
+      <c r="R13" s="1">
+        <v>10</v>
+      </c>
+      <c r="S13" s="1">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" s="1">
+        <v>60</v>
+      </c>
+      <c r="D14" s="1">
+        <v>86</v>
+      </c>
+      <c r="E14" s="1">
+        <v>14</v>
+      </c>
+      <c r="F14" s="1">
+        <v>0</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
+        <v>0</v>
+      </c>
+      <c r="I14" s="1">
+        <v>0</v>
+      </c>
+      <c r="J14" s="1">
+        <v>0</v>
+      </c>
+      <c r="K14" s="1">
+        <v>0</v>
+      </c>
+      <c r="L14" s="1">
+        <v>0</v>
+      </c>
+      <c r="M14" s="1">
+        <v>0</v>
+      </c>
+      <c r="N14" s="1">
+        <v>0</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P14" s="1">
+        <v>662</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>464</v>
+      </c>
+      <c r="R14" s="1">
+        <v>7.41</v>
+      </c>
+      <c r="S14" s="1">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="1">
+        <v>26</v>
+      </c>
+      <c r="D15" s="1">
+        <v>80</v>
+      </c>
+      <c r="E15" s="1">
+        <v>20</v>
+      </c>
+      <c r="F15" s="1">
+        <v>0</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1">
+        <v>0</v>
+      </c>
+      <c r="I15" s="1">
+        <v>0</v>
+      </c>
+      <c r="J15" s="1">
+        <v>0</v>
+      </c>
+      <c r="K15" s="1">
+        <v>0</v>
+      </c>
+      <c r="L15" s="1">
+        <v>0</v>
+      </c>
+      <c r="M15" s="1">
+        <v>0</v>
+      </c>
+      <c r="N15" s="1">
+        <v>0</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P15" s="1">
+        <v>677</v>
+      </c>
+      <c r="Q15" s="1">
+        <v>516</v>
+      </c>
+      <c r="R15" s="1">
+        <v>6.48</v>
+      </c>
+      <c r="S15" s="1">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" s="1">
+        <v>13</v>
+      </c>
+      <c r="D16" s="1">
+        <v>100</v>
+      </c>
+      <c r="E16" s="1">
+        <v>0</v>
+      </c>
+      <c r="F16" s="1">
+        <v>0</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1">
+        <v>0</v>
+      </c>
+      <c r="I16" s="1">
+        <v>0</v>
+      </c>
+      <c r="J16" s="1">
+        <v>0</v>
+      </c>
+      <c r="K16" s="1">
+        <v>0</v>
+      </c>
+      <c r="L16" s="1">
+        <v>0</v>
+      </c>
+      <c r="M16" s="1">
+        <v>0</v>
+      </c>
+      <c r="N16" s="1">
+        <v>0</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P16" s="1">
+        <v>728</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>822</v>
+      </c>
+      <c r="R16" s="1">
+        <v>10</v>
+      </c>
+      <c r="S16" s="1">
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="1">
+        <v>25</v>
+      </c>
+      <c r="D17" s="1">
+        <v>89</v>
+      </c>
+      <c r="E17" s="1">
+        <v>11</v>
+      </c>
+      <c r="F17" s="1">
+        <v>0</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0</v>
+      </c>
+      <c r="I17" s="1">
+        <v>0</v>
+      </c>
+      <c r="J17" s="1">
+        <v>0</v>
+      </c>
+      <c r="K17" s="1">
+        <v>0</v>
+      </c>
+      <c r="L17" s="1">
+        <v>0</v>
+      </c>
+      <c r="M17" s="1">
+        <v>0</v>
+      </c>
+      <c r="N17" s="1">
+        <v>0</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P17" s="1">
+        <v>742</v>
+      </c>
+      <c r="Q17" s="1">
+        <v>672</v>
+      </c>
+      <c r="R17" s="1">
+        <v>7.83</v>
+      </c>
+      <c r="S17" s="1">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" s="1">
+        <v>20</v>
+      </c>
+      <c r="D18" s="1">
+        <v>86</v>
+      </c>
+      <c r="E18" s="1">
+        <v>14</v>
+      </c>
+      <c r="F18" s="1">
+        <v>0</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1">
+        <v>0</v>
+      </c>
+      <c r="I18" s="1">
+        <v>0</v>
+      </c>
+      <c r="J18" s="1">
+        <v>0</v>
+      </c>
+      <c r="K18" s="1">
+        <v>0</v>
+      </c>
+      <c r="L18" s="1">
+        <v>0</v>
+      </c>
+      <c r="M18" s="1">
+        <v>0</v>
+      </c>
+      <c r="N18" s="1">
+        <v>0</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P18" s="1">
+        <v>814</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>694</v>
+      </c>
+      <c r="R18" s="1">
+        <v>7.41</v>
+      </c>
+      <c r="S18" s="1">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19" t="s">
+        <v>49</v>
+      </c>
+      <c r="C19" s="1">
+        <v>25</v>
+      </c>
+      <c r="D19" s="1">
+        <v>79</v>
+      </c>
+      <c r="E19" s="1">
+        <v>21</v>
+      </c>
+      <c r="F19" s="1">
+        <v>0</v>
+      </c>
+      <c r="G19" s="1">
+        <v>0</v>
+      </c>
+      <c r="H19" s="1">
+        <v>0</v>
+      </c>
+      <c r="I19" s="1">
+        <v>0</v>
+      </c>
+      <c r="J19" s="1">
+        <v>0</v>
+      </c>
+      <c r="K19" s="1">
+        <v>0</v>
+      </c>
+      <c r="L19" s="1">
+        <v>0</v>
+      </c>
+      <c r="M19" s="1">
+        <v>0</v>
+      </c>
+      <c r="N19" s="1">
+        <v>0</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P19" s="1">
+        <v>817</v>
+      </c>
+      <c r="Q19" s="1">
+        <v>630</v>
+      </c>
+      <c r="R19" s="1">
+        <v>6.39</v>
+      </c>
+      <c r="S19" s="1">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="1">
+        <v>28</v>
+      </c>
+      <c r="D20" s="1">
+        <v>81</v>
+      </c>
+      <c r="E20" s="1">
+        <v>19</v>
+      </c>
+      <c r="F20" s="1">
+        <v>0</v>
+      </c>
+      <c r="G20" s="1">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1">
+        <v>0</v>
+      </c>
+      <c r="I20" s="1">
+        <v>0</v>
+      </c>
+      <c r="J20" s="1">
+        <v>0</v>
+      </c>
+      <c r="K20" s="1">
+        <v>0</v>
+      </c>
+      <c r="L20" s="1">
+        <v>0</v>
+      </c>
+      <c r="M20" s="1">
+        <v>0</v>
+      </c>
+      <c r="N20" s="1">
+        <v>0</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P20" s="1">
+        <v>937</v>
+      </c>
+      <c r="Q20" s="1">
+        <v>763</v>
+      </c>
+      <c r="R20" s="1">
+        <v>6.65</v>
+      </c>
+      <c r="S20" s="1">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>52</v>
+      </c>
+      <c r="B21" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" s="1">
+        <v>24</v>
+      </c>
+      <c r="D21" s="1">
+        <v>70</v>
+      </c>
+      <c r="E21" s="1">
+        <v>30</v>
+      </c>
+      <c r="F21" s="1">
+        <v>0</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0</v>
+      </c>
+      <c r="H21" s="1">
+        <v>0</v>
+      </c>
+      <c r="I21" s="1">
+        <v>0</v>
+      </c>
+      <c r="J21" s="1">
+        <v>0</v>
+      </c>
+      <c r="K21" s="1">
+        <v>0</v>
+      </c>
+      <c r="L21" s="1">
+        <v>0</v>
+      </c>
+      <c r="M21" s="1">
+        <v>0</v>
+      </c>
+      <c r="N21" s="1">
+        <v>0</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P21" s="1">
+        <v>971</v>
+      </c>
+      <c r="Q21" s="1">
+        <v>672</v>
+      </c>
+      <c r="R21" s="1">
+        <v>5.38</v>
+      </c>
+      <c r="S21" s="1">
+        <v>1502</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>54</v>
+      </c>
+      <c r="B22" t="s">
+        <v>55</v>
+      </c>
+      <c r="C22" s="1">
+        <v>12</v>
+      </c>
+      <c r="D22" s="1">
+        <v>79</v>
+      </c>
+      <c r="E22" s="1">
+        <v>21</v>
+      </c>
+      <c r="F22" s="1">
+        <v>0</v>
+      </c>
+      <c r="G22" s="1">
+        <v>0</v>
+      </c>
+      <c r="H22" s="1">
+        <v>0</v>
+      </c>
+      <c r="I22" s="1">
+        <v>0</v>
+      </c>
+      <c r="J22" s="1">
+        <v>0</v>
+      </c>
+      <c r="K22" s="1">
+        <v>0</v>
+      </c>
+      <c r="L22" s="1">
+        <v>0</v>
+      </c>
+      <c r="M22" s="1">
+        <v>0</v>
+      </c>
+      <c r="N22" s="1">
+        <v>0</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P22" s="1">
+        <v>976</v>
+      </c>
+      <c r="Q22" s="1">
+        <v>900</v>
+      </c>
+      <c r="R22" s="1">
+        <v>6.3</v>
+      </c>
+      <c r="S22" s="1">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" t="s">
+        <v>57</v>
+      </c>
+      <c r="C23" s="1">
+        <v>70</v>
+      </c>
+      <c r="D23" s="1">
+        <v>67</v>
+      </c>
+      <c r="E23" s="1">
+        <v>33</v>
+      </c>
+      <c r="F23" s="1">
+        <v>0</v>
+      </c>
+      <c r="G23" s="1">
+        <v>0</v>
+      </c>
+      <c r="H23" s="1">
+        <v>0</v>
+      </c>
+      <c r="I23" s="1">
+        <v>0</v>
+      </c>
+      <c r="J23" s="1">
+        <v>0</v>
+      </c>
+      <c r="K23" s="1">
+        <v>0</v>
+      </c>
+      <c r="L23" s="1">
+        <v>0</v>
+      </c>
+      <c r="M23" s="1">
+        <v>0</v>
+      </c>
+      <c r="N23" s="1">
+        <v>0</v>
+      </c>
+      <c r="O23" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P23" s="1">
+        <v>983</v>
+      </c>
+      <c r="Q23" s="1">
+        <v>618</v>
+      </c>
+      <c r="R23" s="1">
+        <v>5.1100000000000003</v>
+      </c>
+      <c r="S23" s="1">
+        <v>1595</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>58</v>
+      </c>
+      <c r="B24" t="s">
+        <v>59</v>
+      </c>
+      <c r="C24" s="1">
+        <v>18</v>
+      </c>
+      <c r="D24" s="1">
+        <v>73</v>
+      </c>
+      <c r="E24" s="1">
+        <v>27</v>
+      </c>
+      <c r="F24" s="1">
+        <v>0</v>
+      </c>
+      <c r="G24" s="1">
+        <v>0</v>
+      </c>
+      <c r="H24" s="1">
+        <v>0</v>
+      </c>
+      <c r="I24" s="1">
+        <v>0</v>
+      </c>
+      <c r="J24" s="1">
+        <v>0</v>
+      </c>
+      <c r="K24" s="1">
+        <v>0</v>
+      </c>
+      <c r="L24" s="1">
+        <v>0</v>
+      </c>
+      <c r="M24" s="1">
+        <v>0</v>
+      </c>
+      <c r="N24" s="1">
+        <v>0</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P24" s="1">
+        <v>987</v>
+      </c>
+      <c r="Q24" s="1">
+        <v>849</v>
+      </c>
+      <c r="R24" s="1">
+        <v>5.64</v>
+      </c>
+      <c r="S24" s="1">
+        <v>1418</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>62</v>
+      </c>
+      <c r="B25" t="s">
+        <v>63</v>
+      </c>
+      <c r="C25" s="1">
+        <v>17</v>
+      </c>
+      <c r="D25" s="1">
+        <v>71</v>
+      </c>
+      <c r="E25" s="1">
+        <v>29</v>
+      </c>
+      <c r="F25" s="1">
+        <v>0</v>
+      </c>
+      <c r="G25" s="1">
+        <v>0</v>
+      </c>
+      <c r="H25" s="1">
+        <v>0</v>
+      </c>
+      <c r="I25" s="1">
+        <v>0</v>
+      </c>
+      <c r="J25" s="1">
+        <v>0</v>
+      </c>
+      <c r="K25" s="1">
+        <v>0</v>
+      </c>
+      <c r="L25" s="1">
+        <v>0</v>
+      </c>
+      <c r="M25" s="1">
+        <v>0</v>
+      </c>
+      <c r="N25" s="1">
+        <v>0</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P25" s="1">
+        <v>990</v>
+      </c>
+      <c r="Q25" s="1">
+        <v>623</v>
+      </c>
+      <c r="R25" s="1">
+        <v>5.51</v>
+      </c>
+      <c r="S25" s="1">
+        <v>1397</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>60</v>
+      </c>
+      <c r="B26" t="s">
+        <v>61</v>
+      </c>
+      <c r="C26" s="1">
+        <v>64</v>
+      </c>
+      <c r="D26" s="1">
+        <v>79</v>
+      </c>
+      <c r="E26" s="1">
+        <v>8</v>
+      </c>
+      <c r="F26" s="1">
+        <v>14</v>
+      </c>
+      <c r="G26" s="1">
+        <v>0</v>
+      </c>
+      <c r="H26" s="1">
+        <v>0</v>
+      </c>
+      <c r="I26" s="1">
+        <v>0</v>
+      </c>
+      <c r="J26" s="1">
+        <v>0</v>
+      </c>
+      <c r="K26" s="1">
+        <v>0</v>
+      </c>
+      <c r="L26" s="1">
+        <v>0</v>
+      </c>
+      <c r="M26" s="1">
+        <v>0</v>
+      </c>
+      <c r="N26" s="1">
+        <v>0</v>
+      </c>
+      <c r="O26" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P26" s="1">
+        <v>1041</v>
+      </c>
+      <c r="Q26" s="1">
+        <v>585</v>
+      </c>
+      <c r="R26" s="1">
+        <v>6.08</v>
+      </c>
+      <c r="S26" s="1">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>64</v>
+      </c>
+      <c r="B27" t="s">
+        <v>65</v>
+      </c>
+      <c r="C27" s="1">
+        <v>35</v>
+      </c>
+      <c r="D27" s="1">
+        <v>67</v>
+      </c>
+      <c r="E27" s="1">
+        <v>33</v>
+      </c>
+      <c r="F27" s="1">
+        <v>0</v>
+      </c>
+      <c r="G27" s="1">
+        <v>0</v>
+      </c>
+      <c r="H27" s="1">
+        <v>0</v>
+      </c>
+      <c r="I27" s="1">
+        <v>0</v>
+      </c>
+      <c r="J27" s="1">
+        <v>0</v>
+      </c>
+      <c r="K27" s="1">
+        <v>0</v>
+      </c>
+      <c r="L27" s="1">
+        <v>0</v>
+      </c>
+      <c r="M27" s="1">
+        <v>0</v>
+      </c>
+      <c r="N27" s="1">
+        <v>0</v>
+      </c>
+      <c r="O27" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P27" s="1">
+        <v>1048</v>
+      </c>
+      <c r="Q27" s="1">
+        <v>900</v>
+      </c>
+      <c r="R27" s="1">
+        <v>5.1100000000000003</v>
+      </c>
+      <c r="S27" s="1">
+        <v>1431</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>66</v>
+      </c>
+      <c r="B28" t="s">
+        <v>67</v>
+      </c>
+      <c r="C28" s="1">
+        <v>55</v>
+      </c>
+      <c r="D28" s="1">
+        <v>72</v>
+      </c>
+      <c r="E28" s="1">
+        <v>13</v>
+      </c>
+      <c r="F28" s="1">
+        <v>15</v>
+      </c>
+      <c r="G28" s="1">
+        <v>0</v>
+      </c>
+      <c r="H28" s="1">
+        <v>0</v>
+      </c>
+      <c r="I28" s="1">
+        <v>0</v>
+      </c>
+      <c r="J28" s="1">
+        <v>0</v>
+      </c>
+      <c r="K28" s="1">
+        <v>0</v>
+      </c>
+      <c r="L28" s="1">
+        <v>0</v>
+      </c>
+      <c r="M28" s="1">
+        <v>0</v>
+      </c>
+      <c r="N28" s="1">
+        <v>0</v>
+      </c>
+      <c r="O28" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P28" s="1">
+        <v>1129</v>
+      </c>
+      <c r="Q28" s="1">
+        <v>437</v>
+      </c>
+      <c r="R28" s="1">
+        <v>5.18</v>
+      </c>
+      <c r="S28" s="1">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>68</v>
+      </c>
+      <c r="B29" t="s">
+        <v>69</v>
+      </c>
+      <c r="C29" s="1">
+        <v>17</v>
+      </c>
+      <c r="D29" s="1">
+        <v>61</v>
+      </c>
+      <c r="E29" s="1">
+        <v>39</v>
+      </c>
+      <c r="F29" s="1">
+        <v>0</v>
+      </c>
+      <c r="G29" s="1">
+        <v>0</v>
+      </c>
+      <c r="H29" s="1">
+        <v>0</v>
+      </c>
+      <c r="I29" s="1">
+        <v>0</v>
+      </c>
+      <c r="J29" s="1">
+        <v>0</v>
+      </c>
+      <c r="K29" s="1">
+        <v>0</v>
+      </c>
+      <c r="L29" s="1">
+        <v>0</v>
+      </c>
+      <c r="M29" s="1">
+        <v>0</v>
+      </c>
+      <c r="N29" s="1">
+        <v>0</v>
+      </c>
+      <c r="O29" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P29" s="1">
+        <v>1158</v>
+      </c>
+      <c r="Q29" s="1">
+        <v>1090</v>
+      </c>
+      <c r="R29" s="1">
+        <v>4.76</v>
+      </c>
+      <c r="S29" s="1">
+        <v>1501</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>70</v>
+      </c>
+      <c r="B30" t="s">
+        <v>71</v>
+      </c>
+      <c r="C30" s="1">
+        <v>6</v>
+      </c>
+      <c r="D30" s="1">
+        <v>63</v>
+      </c>
+      <c r="E30" s="1">
+        <v>38</v>
+      </c>
+      <c r="F30" s="1">
+        <v>0</v>
+      </c>
+      <c r="G30" s="1">
+        <v>0</v>
+      </c>
+      <c r="H30" s="1">
+        <v>0</v>
+      </c>
+      <c r="I30" s="1">
+        <v>0</v>
+      </c>
+      <c r="J30" s="1">
+        <v>0</v>
+      </c>
+      <c r="K30" s="1">
+        <v>0</v>
+      </c>
+      <c r="L30" s="1">
+        <v>0</v>
+      </c>
+      <c r="M30" s="1">
+        <v>0</v>
+      </c>
+      <c r="N30" s="1">
+        <v>0</v>
+      </c>
+      <c r="O30" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P30" s="1">
+        <v>1176</v>
+      </c>
+      <c r="Q30" s="1">
+        <v>1140</v>
+      </c>
+      <c r="R30" s="1">
+        <v>4.84</v>
+      </c>
+      <c r="S30" s="1">
+        <v>1398</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>72</v>
+      </c>
+      <c r="B31" t="s">
+        <v>73</v>
+      </c>
+      <c r="C31" s="1">
+        <v>19</v>
+      </c>
+      <c r="D31" s="1">
+        <v>64</v>
+      </c>
+      <c r="E31" s="1">
+        <v>36</v>
+      </c>
+      <c r="F31" s="1">
+        <v>0</v>
+      </c>
+      <c r="G31" s="1">
+        <v>0</v>
+      </c>
+      <c r="H31" s="1">
+        <v>0</v>
+      </c>
+      <c r="I31" s="1">
+        <v>0</v>
+      </c>
+      <c r="J31" s="1">
+        <v>0</v>
+      </c>
+      <c r="K31" s="1">
+        <v>0</v>
+      </c>
+      <c r="L31" s="1">
+        <v>0</v>
+      </c>
+      <c r="M31" s="1">
+        <v>0</v>
+      </c>
+      <c r="N31" s="1">
+        <v>0</v>
+      </c>
+      <c r="O31" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P31" s="1">
+        <v>1207</v>
+      </c>
+      <c r="Q31" s="1">
+        <v>824</v>
+      </c>
+      <c r="R31" s="1">
+        <v>4.93</v>
+      </c>
+      <c r="S31" s="1">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>74</v>
+      </c>
+      <c r="B32" t="s">
+        <v>75</v>
+      </c>
+      <c r="C32" s="1">
+        <v>11</v>
+      </c>
+      <c r="D32" s="1">
+        <v>47</v>
+      </c>
+      <c r="E32" s="1">
+        <v>53</v>
+      </c>
+      <c r="F32" s="1">
+        <v>0</v>
+      </c>
+      <c r="G32" s="1">
+        <v>0</v>
+      </c>
+      <c r="H32" s="1">
+        <v>0</v>
+      </c>
+      <c r="I32" s="1">
+        <v>0</v>
+      </c>
+      <c r="J32" s="1">
+        <v>0</v>
+      </c>
+      <c r="K32" s="1">
+        <v>0</v>
+      </c>
+      <c r="L32" s="1">
+        <v>0</v>
+      </c>
+      <c r="M32" s="1">
+        <v>0</v>
+      </c>
+      <c r="N32" s="1">
+        <v>0</v>
+      </c>
+      <c r="O32" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P32" s="1">
+        <v>1213</v>
+      </c>
+      <c r="Q32" s="1">
+        <v>945</v>
+      </c>
+      <c r="R32" s="1">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="S32" s="1">
+        <v>1662</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>78</v>
+      </c>
+      <c r="B33" t="s">
+        <v>79</v>
+      </c>
+      <c r="C33" s="1">
+        <v>7</v>
+      </c>
+      <c r="D33" s="1">
+        <v>45</v>
+      </c>
+      <c r="E33" s="1">
+        <v>55</v>
+      </c>
+      <c r="F33" s="1">
+        <v>0</v>
+      </c>
+      <c r="G33" s="1">
+        <v>0</v>
+      </c>
+      <c r="H33" s="1">
+        <v>0</v>
+      </c>
+      <c r="I33" s="1">
+        <v>0</v>
+      </c>
+      <c r="J33" s="1">
+        <v>0</v>
+      </c>
+      <c r="K33" s="1">
+        <v>0</v>
+      </c>
+      <c r="L33" s="1">
+        <v>0</v>
+      </c>
+      <c r="M33" s="1">
+        <v>0</v>
+      </c>
+      <c r="N33" s="1">
+        <v>0</v>
+      </c>
+      <c r="O33" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P33" s="1">
+        <v>1276</v>
+      </c>
+      <c r="Q33" s="1">
+        <v>802</v>
+      </c>
+      <c r="R33" s="1">
+        <v>4.55</v>
+      </c>
+      <c r="S33" s="1">
+        <v>1683</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>76</v>
+      </c>
+      <c r="B34" t="s">
+        <v>77</v>
+      </c>
+      <c r="C34" s="1">
+        <v>42</v>
+      </c>
+      <c r="D34" s="1">
+        <v>70</v>
+      </c>
+      <c r="E34" s="1">
+        <v>11</v>
+      </c>
+      <c r="F34" s="1">
+        <v>19</v>
+      </c>
+      <c r="G34" s="1">
+        <v>0</v>
+      </c>
+      <c r="H34" s="1">
+        <v>0</v>
+      </c>
+      <c r="I34" s="1">
+        <v>0</v>
+      </c>
+      <c r="J34" s="1">
+        <v>0</v>
+      </c>
+      <c r="K34" s="1">
+        <v>0</v>
+      </c>
+      <c r="L34" s="1">
+        <v>0</v>
+      </c>
+      <c r="M34" s="1">
+        <v>0</v>
+      </c>
+      <c r="N34" s="1">
+        <v>0</v>
+      </c>
+      <c r="O34" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P34" s="1">
+        <v>1324</v>
+      </c>
+      <c r="Q34" s="1">
+        <v>719</v>
+      </c>
+      <c r="R34" s="1">
+        <v>4.95</v>
+      </c>
+      <c r="S34" s="1">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>84</v>
+      </c>
+      <c r="B35" t="s">
+        <v>85</v>
+      </c>
+      <c r="C35" s="1">
+        <v>13</v>
+      </c>
+      <c r="D35" s="1">
+        <v>43</v>
+      </c>
+      <c r="E35" s="1">
+        <v>57</v>
+      </c>
+      <c r="F35" s="1">
+        <v>0</v>
+      </c>
+      <c r="G35" s="1">
+        <v>0</v>
+      </c>
+      <c r="H35" s="1">
+        <v>0</v>
+      </c>
+      <c r="I35" s="1">
+        <v>0</v>
+      </c>
+      <c r="J35" s="1">
+        <v>0</v>
+      </c>
+      <c r="K35" s="1">
+        <v>0</v>
+      </c>
+      <c r="L35" s="1">
+        <v>0</v>
+      </c>
+      <c r="M35" s="1">
+        <v>0</v>
+      </c>
+      <c r="N35" s="1">
+        <v>0</v>
+      </c>
+      <c r="O35" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P35" s="1">
+        <v>1441</v>
+      </c>
+      <c r="Q35" s="1">
+        <v>1283</v>
+      </c>
+      <c r="R35" s="1">
+        <v>4.6100000000000003</v>
+      </c>
+      <c r="S35" s="1">
+        <v>1824</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>86</v>
+      </c>
+      <c r="B36" t="s">
+        <v>87</v>
+      </c>
+      <c r="C36" s="1">
+        <v>13</v>
+      </c>
+      <c r="D36" s="1">
+        <v>35</v>
+      </c>
+      <c r="E36" s="1">
+        <v>65</v>
+      </c>
+      <c r="F36" s="1">
+        <v>0</v>
+      </c>
+      <c r="G36" s="1">
+        <v>0</v>
+      </c>
+      <c r="H36" s="1">
+        <v>0</v>
+      </c>
+      <c r="I36" s="1">
+        <v>0</v>
+      </c>
+      <c r="J36" s="1">
+        <v>0</v>
+      </c>
+      <c r="K36" s="1">
+        <v>0</v>
+      </c>
+      <c r="L36" s="1">
+        <v>0</v>
+      </c>
+      <c r="M36" s="1">
+        <v>0</v>
+      </c>
+      <c r="N36" s="1">
+        <v>0</v>
+      </c>
+      <c r="O36" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P36" s="1">
+        <v>1446</v>
+      </c>
+      <c r="Q36" s="1">
+        <v>1207</v>
+      </c>
+      <c r="R36" s="1">
+        <v>5.01</v>
+      </c>
+      <c r="S36" s="1">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>82</v>
+      </c>
+      <c r="B37" t="s">
+        <v>83</v>
+      </c>
+      <c r="C37" s="1">
+        <v>53</v>
+      </c>
+      <c r="D37" s="1">
+        <v>49</v>
+      </c>
+      <c r="E37" s="1">
+        <v>39</v>
+      </c>
+      <c r="F37" s="1">
+        <v>12</v>
+      </c>
+      <c r="G37" s="1">
+        <v>0</v>
+      </c>
+      <c r="H37" s="1">
+        <v>0</v>
+      </c>
+      <c r="I37" s="1">
+        <v>0</v>
+      </c>
+      <c r="J37" s="1">
+        <v>0</v>
+      </c>
+      <c r="K37" s="1">
+        <v>0</v>
+      </c>
+      <c r="L37" s="1">
+        <v>0</v>
+      </c>
+      <c r="M37" s="1">
+        <v>0</v>
+      </c>
+      <c r="N37" s="1">
+        <v>0</v>
+      </c>
+      <c r="O37" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P37" s="1">
+        <v>1491</v>
+      </c>
+      <c r="Q37" s="1">
+        <v>805</v>
+      </c>
+      <c r="R37" s="1">
+        <v>3.44</v>
+      </c>
+      <c r="S37" s="1">
+        <v>2254</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>80</v>
+      </c>
+      <c r="B38" t="s">
+        <v>81</v>
+      </c>
+      <c r="C38" s="1">
+        <v>25</v>
+      </c>
+      <c r="D38" s="1">
+        <v>57</v>
+      </c>
+      <c r="E38" s="1">
+        <v>16</v>
+      </c>
+      <c r="F38" s="1">
+        <v>27</v>
+      </c>
+      <c r="G38" s="1">
+        <v>0</v>
+      </c>
+      <c r="H38" s="1">
+        <v>0</v>
+      </c>
+      <c r="I38" s="1">
+        <v>0</v>
+      </c>
+      <c r="J38" s="1">
+        <v>0</v>
+      </c>
+      <c r="K38" s="1">
+        <v>0</v>
+      </c>
+      <c r="L38" s="1">
+        <v>0</v>
+      </c>
+      <c r="M38" s="1">
+        <v>0</v>
+      </c>
+      <c r="N38" s="1">
+        <v>0</v>
+      </c>
+      <c r="O38" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P38" s="1">
+        <v>1513</v>
+      </c>
+      <c r="Q38" s="1">
+        <v>543</v>
+      </c>
+      <c r="R38" s="1">
+        <v>3.68</v>
+      </c>
+      <c r="S38" s="1">
+        <v>1388</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>90</v>
+      </c>
+      <c r="B39" t="s">
+        <v>91</v>
+      </c>
+      <c r="C39" s="1">
+        <v>12</v>
+      </c>
+      <c r="D39" s="1">
+        <v>40</v>
+      </c>
+      <c r="E39" s="1">
+        <v>60</v>
+      </c>
+      <c r="F39" s="1">
+        <v>0</v>
+      </c>
+      <c r="G39" s="1">
+        <v>0</v>
+      </c>
+      <c r="H39" s="1">
+        <v>0</v>
+      </c>
+      <c r="I39" s="1">
+        <v>0</v>
+      </c>
+      <c r="J39" s="1">
+        <v>0</v>
+      </c>
+      <c r="K39" s="1">
+        <v>0</v>
+      </c>
+      <c r="L39" s="1">
+        <v>0</v>
+      </c>
+      <c r="M39" s="1">
+        <v>0</v>
+      </c>
+      <c r="N39" s="1">
+        <v>0</v>
+      </c>
+      <c r="O39" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P39" s="1">
+        <v>1540</v>
+      </c>
+      <c r="Q39" s="1">
+        <v>1280</v>
+      </c>
+      <c r="R39" s="1">
+        <v>4.72</v>
+      </c>
+      <c r="S39" s="1">
+        <v>1946</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>94</v>
+      </c>
+      <c r="B40" t="s">
+        <v>95</v>
+      </c>
+      <c r="C40" s="1">
+        <v>8</v>
+      </c>
+      <c r="D40" s="1">
+        <v>50</v>
+      </c>
+      <c r="E40" s="1">
+        <v>50</v>
+      </c>
+      <c r="F40" s="1">
+        <v>0</v>
+      </c>
+      <c r="G40" s="1">
+        <v>0</v>
+      </c>
+      <c r="H40" s="1">
+        <v>0</v>
+      </c>
+      <c r="I40" s="1">
+        <v>0</v>
+      </c>
+      <c r="J40" s="1">
+        <v>0</v>
+      </c>
+      <c r="K40" s="1">
+        <v>0</v>
+      </c>
+      <c r="L40" s="1">
+        <v>0</v>
+      </c>
+      <c r="M40" s="1">
+        <v>0</v>
+      </c>
+      <c r="N40" s="1">
+        <v>0</v>
+      </c>
+      <c r="O40" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P40" s="1">
+        <v>1608</v>
+      </c>
+      <c r="Q40" s="1">
+        <v>1020</v>
+      </c>
+      <c r="R40" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="S40" s="1">
+        <v>2392</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>96</v>
+      </c>
+      <c r="B41" t="s">
+        <v>97</v>
+      </c>
+      <c r="C41" s="1">
+        <v>19</v>
+      </c>
+      <c r="D41" s="1">
+        <v>27</v>
+      </c>
+      <c r="E41" s="1">
+        <v>73</v>
+      </c>
+      <c r="F41" s="1">
+        <v>0</v>
+      </c>
+      <c r="G41" s="1">
+        <v>0</v>
+      </c>
+      <c r="H41" s="1">
+        <v>0</v>
+      </c>
+      <c r="I41" s="1">
+        <v>0</v>
+      </c>
+      <c r="J41" s="1">
+        <v>0</v>
+      </c>
+      <c r="K41" s="1">
+        <v>0</v>
+      </c>
+      <c r="L41" s="1">
+        <v>0</v>
+      </c>
+      <c r="M41" s="1">
+        <v>0</v>
+      </c>
+      <c r="N41" s="1">
+        <v>0</v>
+      </c>
+      <c r="O41" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P41" s="1">
+        <v>1612</v>
+      </c>
+      <c r="Q41" s="1">
+        <v>1387</v>
+      </c>
+      <c r="R41" s="1">
+        <v>5.66</v>
+      </c>
+      <c r="S41" s="1">
+        <v>2038</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>92</v>
+      </c>
+      <c r="B42" t="s">
+        <v>93</v>
+      </c>
+      <c r="C42" s="1">
+        <v>32</v>
+      </c>
+      <c r="D42" s="1">
+        <v>50</v>
+      </c>
+      <c r="E42" s="1">
+        <v>29</v>
+      </c>
+      <c r="F42" s="1">
+        <v>20</v>
+      </c>
+      <c r="G42" s="1">
+        <v>0</v>
+      </c>
+      <c r="H42" s="1">
+        <v>0</v>
+      </c>
+      <c r="I42" s="1">
+        <v>0</v>
+      </c>
+      <c r="J42" s="1">
+        <v>0</v>
+      </c>
+      <c r="K42" s="1">
+        <v>0</v>
+      </c>
+      <c r="L42" s="1">
+        <v>0</v>
+      </c>
+      <c r="M42" s="1">
+        <v>0</v>
+      </c>
+      <c r="N42" s="1">
+        <v>0</v>
+      </c>
+      <c r="O42" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P42" s="1">
+        <v>1634</v>
+      </c>
+      <c r="Q42" s="1">
+        <v>950</v>
+      </c>
+      <c r="R42" s="1">
+        <v>3.19</v>
+      </c>
+      <c r="S42" s="1">
+        <v>1915</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>88</v>
+      </c>
+      <c r="B43" t="s">
+        <v>89</v>
+      </c>
+      <c r="C43" s="1">
+        <v>28</v>
+      </c>
+      <c r="D43" s="1">
+        <v>60</v>
+      </c>
+      <c r="E43" s="1">
+        <v>14</v>
+      </c>
+      <c r="F43" s="1">
+        <v>25</v>
+      </c>
+      <c r="G43" s="1">
+        <v>0</v>
+      </c>
+      <c r="H43" s="1">
+        <v>0</v>
+      </c>
+      <c r="I43" s="1">
+        <v>0</v>
+      </c>
+      <c r="J43" s="1">
+        <v>0</v>
+      </c>
+      <c r="K43" s="1">
+        <v>0</v>
+      </c>
+      <c r="L43" s="1">
+        <v>0</v>
+      </c>
+      <c r="M43" s="1">
+        <v>0</v>
+      </c>
+      <c r="N43" s="1">
+        <v>0</v>
+      </c>
+      <c r="O43" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P43" s="1">
+        <v>1734</v>
+      </c>
+      <c r="Q43" s="1">
+        <v>750</v>
+      </c>
+      <c r="R43" s="1">
+        <v>3.93</v>
+      </c>
+      <c r="S43" s="1">
+        <v>1382</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>98</v>
+      </c>
+      <c r="B44" t="s">
+        <v>99</v>
+      </c>
+      <c r="C44" s="1">
+        <v>67</v>
+      </c>
+      <c r="D44" s="1">
+        <v>45</v>
+      </c>
+      <c r="E44" s="1">
+        <v>37</v>
+      </c>
+      <c r="F44" s="1">
+        <v>18</v>
+      </c>
+      <c r="G44" s="1">
+        <v>0</v>
+      </c>
+      <c r="H44" s="1">
+        <v>0</v>
+      </c>
+      <c r="I44" s="1">
+        <v>0</v>
+      </c>
+      <c r="J44" s="1">
+        <v>0</v>
+      </c>
+      <c r="K44" s="1">
+        <v>0</v>
+      </c>
+      <c r="L44" s="1">
+        <v>0</v>
+      </c>
+      <c r="M44" s="1">
+        <v>0</v>
+      </c>
+      <c r="N44" s="1">
+        <v>0</v>
+      </c>
+      <c r="O44" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P44" s="1">
+        <v>1761</v>
+      </c>
+      <c r="Q44" s="1">
+        <v>1193</v>
+      </c>
+      <c r="R44" s="1">
+        <v>3.07</v>
+      </c>
+      <c r="S44" s="1">
+        <v>1931</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>106</v>
+      </c>
+      <c r="B45" t="s">
+        <v>107</v>
+      </c>
+      <c r="C45" s="1">
+        <v>16</v>
+      </c>
+      <c r="D45" s="1">
+        <v>21</v>
+      </c>
+      <c r="E45" s="1">
+        <v>79</v>
+      </c>
+      <c r="F45" s="1">
+        <v>0</v>
+      </c>
+      <c r="G45" s="1">
+        <v>0</v>
+      </c>
+      <c r="H45" s="1">
+        <v>0</v>
+      </c>
+      <c r="I45" s="1">
+        <v>0</v>
+      </c>
+      <c r="J45" s="1">
+        <v>0</v>
+      </c>
+      <c r="K45" s="1">
+        <v>0</v>
+      </c>
+      <c r="L45" s="1">
+        <v>0</v>
+      </c>
+      <c r="M45" s="1">
+        <v>0</v>
+      </c>
+      <c r="N45" s="1">
+        <v>0</v>
+      </c>
+      <c r="O45" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P45" s="1">
+        <v>1809</v>
+      </c>
+      <c r="Q45" s="1">
+        <v>1625</v>
+      </c>
+      <c r="R45" s="1">
+        <v>6.4</v>
+      </c>
+      <c r="S45" s="1">
+        <v>2285</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>108</v>
+      </c>
+      <c r="B46" t="s">
+        <v>109</v>
+      </c>
+      <c r="C46" s="1">
+        <v>11</v>
+      </c>
+      <c r="D46" s="1">
+        <v>22</v>
+      </c>
+      <c r="E46" s="1">
+        <v>78</v>
+      </c>
+      <c r="F46" s="1">
+        <v>0</v>
+      </c>
+      <c r="G46" s="1">
+        <v>0</v>
+      </c>
+      <c r="H46" s="1">
+        <v>0</v>
+      </c>
+      <c r="I46" s="1">
+        <v>0</v>
+      </c>
+      <c r="J46" s="1">
+        <v>0</v>
+      </c>
+      <c r="K46" s="1">
+        <v>0</v>
+      </c>
+      <c r="L46" s="1">
+        <v>0</v>
+      </c>
+      <c r="M46" s="1">
+        <v>0</v>
+      </c>
+      <c r="N46" s="1">
+        <v>0</v>
+      </c>
+      <c r="O46" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P46" s="1">
+        <v>1814</v>
+      </c>
+      <c r="Q46" s="1">
+        <v>1439</v>
+      </c>
+      <c r="R46" s="1">
+        <v>6.26</v>
+      </c>
+      <c r="S46" s="1">
+        <v>2337</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>102</v>
+      </c>
+      <c r="B47" t="s">
+        <v>103</v>
+      </c>
+      <c r="C47" s="1">
+        <v>34</v>
+      </c>
+      <c r="D47" s="1">
+        <v>31</v>
+      </c>
+      <c r="E47" s="1">
+        <v>53</v>
+      </c>
+      <c r="F47" s="1">
+        <v>16</v>
+      </c>
+      <c r="G47" s="1">
+        <v>0</v>
+      </c>
+      <c r="H47" s="1">
+        <v>0</v>
+      </c>
+      <c r="I47" s="1">
+        <v>0</v>
+      </c>
+      <c r="J47" s="1">
+        <v>0</v>
+      </c>
+      <c r="K47" s="1">
+        <v>0</v>
+      </c>
+      <c r="L47" s="1">
+        <v>0</v>
+      </c>
+      <c r="M47" s="1">
+        <v>0</v>
+      </c>
+      <c r="N47" s="1">
+        <v>0</v>
+      </c>
+      <c r="O47" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P47" s="1">
+        <v>1896</v>
+      </c>
+      <c r="Q47" s="1">
+        <v>1354</v>
+      </c>
+      <c r="R47" s="1">
+        <v>3.46</v>
+      </c>
+      <c r="S47" s="1">
+        <v>1907</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>104</v>
+      </c>
+      <c r="B48" t="s">
+        <v>105</v>
+      </c>
+      <c r="C48" s="1">
+        <v>80</v>
+      </c>
+      <c r="D48" s="1">
+        <v>46</v>
+      </c>
+      <c r="E48" s="1">
+        <v>24</v>
+      </c>
+      <c r="F48" s="1">
+        <v>30</v>
+      </c>
+      <c r="G48" s="1">
+        <v>0</v>
+      </c>
+      <c r="H48" s="1">
+        <v>0</v>
+      </c>
+      <c r="I48" s="1">
+        <v>0</v>
+      </c>
+      <c r="J48" s="1">
+        <v>0</v>
+      </c>
+      <c r="K48" s="1">
+        <v>0</v>
+      </c>
+      <c r="L48" s="1">
+        <v>0</v>
+      </c>
+      <c r="M48" s="1">
+        <v>0</v>
+      </c>
+      <c r="N48" s="1">
+        <v>0</v>
+      </c>
+      <c r="O48" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P48" s="1">
+        <v>1929</v>
+      </c>
+      <c r="Q48" s="1">
+        <v>1054</v>
+      </c>
+      <c r="R48" s="1">
+        <v>2.97</v>
+      </c>
+      <c r="S48" s="1">
+        <v>1687</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>100</v>
+      </c>
+      <c r="B49" t="s">
+        <v>101</v>
+      </c>
+      <c r="C49" s="1">
+        <v>39</v>
+      </c>
+      <c r="D49" s="1">
+        <v>47</v>
+      </c>
+      <c r="E49" s="1">
+        <v>37</v>
+      </c>
+      <c r="F49" s="1">
+        <v>16</v>
+      </c>
+      <c r="G49" s="1">
+        <v>0</v>
+      </c>
+      <c r="H49" s="1">
+        <v>0</v>
+      </c>
+      <c r="I49" s="1">
+        <v>0</v>
+      </c>
+      <c r="J49" s="1">
+        <v>0</v>
+      </c>
+      <c r="K49" s="1">
+        <v>0</v>
+      </c>
+      <c r="L49" s="1">
+        <v>0</v>
+      </c>
+      <c r="M49" s="1">
+        <v>0</v>
+      </c>
+      <c r="N49" s="1">
+        <v>0</v>
+      </c>
+      <c r="O49" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P49" s="1">
+        <v>1970</v>
+      </c>
+      <c r="Q49" s="1">
+        <v>788</v>
+      </c>
+      <c r="R49" s="1">
+        <v>3.19</v>
+      </c>
+      <c r="S49" s="1">
+        <v>2301</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>110</v>
+      </c>
+      <c r="B50" t="s">
+        <v>111</v>
+      </c>
+      <c r="C50" s="1">
+        <v>16</v>
+      </c>
+      <c r="D50" s="1">
+        <v>38</v>
+      </c>
+      <c r="E50" s="1">
+        <v>29</v>
+      </c>
+      <c r="F50" s="1">
+        <v>33</v>
+      </c>
+      <c r="G50" s="1">
+        <v>0</v>
+      </c>
+      <c r="H50" s="1">
+        <v>0</v>
+      </c>
+      <c r="I50" s="1">
+        <v>0</v>
+      </c>
+      <c r="J50" s="1">
+        <v>0</v>
+      </c>
+      <c r="K50" s="1">
+        <v>0</v>
+      </c>
+      <c r="L50" s="1">
+        <v>0</v>
+      </c>
+      <c r="M50" s="1">
+        <v>0</v>
+      </c>
+      <c r="N50" s="1">
+        <v>0</v>
+      </c>
+      <c r="O50" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P50" s="1">
+        <v>1974</v>
+      </c>
+      <c r="Q50" s="1">
+        <v>942</v>
+      </c>
+      <c r="R50" s="1">
+        <v>2.72</v>
+      </c>
+      <c r="S50" s="1">
+        <v>2008</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>112</v>
+      </c>
+      <c r="B51" t="s">
+        <v>113</v>
+      </c>
+      <c r="C51" s="1">
+        <v>26</v>
+      </c>
+      <c r="D51" s="1">
+        <v>45</v>
+      </c>
+      <c r="E51" s="1">
+        <v>12</v>
+      </c>
+      <c r="F51" s="1">
+        <v>43</v>
+      </c>
+      <c r="G51" s="1">
+        <v>0</v>
+      </c>
+      <c r="H51" s="1">
+        <v>0</v>
+      </c>
+      <c r="I51" s="1">
+        <v>0</v>
+      </c>
+      <c r="J51" s="1">
+        <v>0</v>
+      </c>
+      <c r="K51" s="1">
+        <v>0</v>
+      </c>
+      <c r="L51" s="1">
+        <v>0</v>
+      </c>
+      <c r="M51" s="1">
+        <v>0</v>
+      </c>
+      <c r="N51" s="1">
+        <v>0</v>
+      </c>
+      <c r="O51" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P51" s="1">
+        <v>2022</v>
+      </c>
+      <c r="Q51" s="1">
+        <v>1157</v>
+      </c>
+      <c r="R51" s="1">
+        <v>3.4</v>
+      </c>
+      <c r="S51" s="1">
+        <v>1849</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>114</v>
+      </c>
+      <c r="B52" t="s">
+        <v>115</v>
+      </c>
+      <c r="C52" s="1">
+        <v>35</v>
+      </c>
+      <c r="D52" s="1">
+        <v>35</v>
+      </c>
+      <c r="E52" s="1">
+        <v>50</v>
+      </c>
+      <c r="F52" s="1">
+        <v>16</v>
+      </c>
+      <c r="G52" s="1">
+        <v>0</v>
+      </c>
+      <c r="H52" s="1">
+        <v>0</v>
+      </c>
+      <c r="I52" s="1">
+        <v>0</v>
+      </c>
+      <c r="J52" s="1">
+        <v>0</v>
+      </c>
+      <c r="K52" s="1">
+        <v>0</v>
+      </c>
+      <c r="L52" s="1">
+        <v>0</v>
+      </c>
+      <c r="M52" s="1">
+        <v>0</v>
+      </c>
+      <c r="N52" s="1">
+        <v>0</v>
+      </c>
+      <c r="O52" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P52" s="1">
+        <v>2145</v>
+      </c>
+      <c r="Q52" s="1">
+        <v>1405</v>
+      </c>
+      <c r="R52" s="1">
+        <v>3.3</v>
+      </c>
+      <c r="S52" s="1">
+        <v>2059</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>120</v>
+      </c>
+      <c r="B53" t="s">
+        <v>121</v>
+      </c>
+      <c r="C53" s="1">
+        <v>24</v>
+      </c>
+      <c r="D53" s="1">
+        <v>29</v>
+      </c>
+      <c r="E53" s="1">
+        <v>33</v>
+      </c>
+      <c r="F53" s="1">
+        <v>38</v>
+      </c>
+      <c r="G53" s="1">
+        <v>0</v>
+      </c>
+      <c r="H53" s="1">
+        <v>0</v>
+      </c>
+      <c r="I53" s="1">
+        <v>0</v>
+      </c>
+      <c r="J53" s="1">
+        <v>0</v>
+      </c>
+      <c r="K53" s="1">
+        <v>0</v>
+      </c>
+      <c r="L53" s="1">
+        <v>0</v>
+      </c>
+      <c r="M53" s="1">
+        <v>0</v>
+      </c>
+      <c r="N53" s="1">
+        <v>0</v>
+      </c>
+      <c r="O53" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P53" s="1">
+        <v>2241</v>
+      </c>
+      <c r="Q53" s="1">
+        <v>1490</v>
+      </c>
+      <c r="R53" s="1">
+        <v>2.71</v>
+      </c>
+      <c r="S53" s="1">
+        <v>2757</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>122</v>
+      </c>
+      <c r="B54" t="s">
+        <v>123</v>
+      </c>
+      <c r="C54" s="1">
+        <v>26</v>
+      </c>
+      <c r="D54" s="1">
+        <v>19</v>
+      </c>
+      <c r="E54" s="1">
+        <v>49</v>
+      </c>
+      <c r="F54" s="1">
+        <v>31</v>
+      </c>
+      <c r="G54" s="1">
+        <v>0</v>
+      </c>
+      <c r="H54" s="1">
+        <v>0</v>
+      </c>
+      <c r="I54" s="1">
+        <v>0</v>
+      </c>
+      <c r="J54" s="1">
+        <v>0</v>
+      </c>
+      <c r="K54" s="1">
+        <v>0</v>
+      </c>
+      <c r="L54" s="1">
+        <v>0</v>
+      </c>
+      <c r="M54" s="1">
+        <v>0</v>
+      </c>
+      <c r="N54" s="1">
+        <v>0</v>
+      </c>
+      <c r="O54" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P54" s="1">
+        <v>2277</v>
+      </c>
+      <c r="Q54" s="1">
+        <v>1330</v>
+      </c>
+      <c r="R54" s="1">
+        <v>3.16</v>
+      </c>
+      <c r="S54" s="1">
+        <v>2272</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>116</v>
+      </c>
+      <c r="B55" t="s">
+        <v>117</v>
+      </c>
+      <c r="C55" s="1">
+        <v>31</v>
+      </c>
+      <c r="D55" s="1">
+        <v>50</v>
+      </c>
+      <c r="E55" s="1">
+        <v>11</v>
+      </c>
+      <c r="F55" s="1">
+        <v>39</v>
+      </c>
+      <c r="G55" s="1">
+        <v>0</v>
+      </c>
+      <c r="H55" s="1">
+        <v>0</v>
+      </c>
+      <c r="I55" s="1">
+        <v>0</v>
+      </c>
+      <c r="J55" s="1">
+        <v>0</v>
+      </c>
+      <c r="K55" s="1">
+        <v>0</v>
+      </c>
+      <c r="L55" s="1">
+        <v>0</v>
+      </c>
+      <c r="M55" s="1">
+        <v>0</v>
+      </c>
+      <c r="N55" s="1">
+        <v>0</v>
+      </c>
+      <c r="O55" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P55" s="1">
+        <v>2290</v>
+      </c>
+      <c r="Q55" s="1">
+        <v>958</v>
+      </c>
+      <c r="R55" s="1">
+        <v>3.55</v>
+      </c>
+      <c r="S55" s="1">
+        <v>1823</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>118</v>
+      </c>
+      <c r="B56" t="s">
+        <v>119</v>
+      </c>
+      <c r="C56" s="1">
+        <v>15</v>
+      </c>
+      <c r="D56" s="1">
+        <v>36</v>
+      </c>
+      <c r="E56" s="1">
+        <v>30</v>
+      </c>
+      <c r="F56" s="1">
+        <v>34</v>
+      </c>
+      <c r="G56" s="1">
+        <v>0</v>
+      </c>
+      <c r="H56" s="1">
+        <v>0</v>
+      </c>
+      <c r="I56" s="1">
+        <v>0</v>
+      </c>
+      <c r="J56" s="1">
+        <v>0</v>
+      </c>
+      <c r="K56" s="1">
+        <v>0</v>
+      </c>
+      <c r="L56" s="1">
+        <v>0</v>
+      </c>
+      <c r="M56" s="1">
+        <v>0</v>
+      </c>
+      <c r="N56" s="1">
+        <v>0</v>
+      </c>
+      <c r="O56" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P56" s="1">
+        <v>2300</v>
+      </c>
+      <c r="Q56" s="1">
+        <v>1311</v>
+      </c>
+      <c r="R56" s="1">
+        <v>2.69</v>
+      </c>
+      <c r="S56" s="1">
+        <v>2338</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>128</v>
+      </c>
+      <c r="B57" t="s">
+        <v>129</v>
+      </c>
+      <c r="C57" s="1">
+        <v>18</v>
+      </c>
+      <c r="D57" s="1">
+        <v>7</v>
+      </c>
+      <c r="E57" s="1">
+        <v>59</v>
+      </c>
+      <c r="F57" s="1">
+        <v>34</v>
+      </c>
+      <c r="G57" s="1">
+        <v>0</v>
+      </c>
+      <c r="H57" s="1">
+        <v>0</v>
+      </c>
+      <c r="I57" s="1">
+        <v>0</v>
+      </c>
+      <c r="J57" s="1">
+        <v>0</v>
+      </c>
+      <c r="K57" s="1">
+        <v>0</v>
+      </c>
+      <c r="L57" s="1">
+        <v>0</v>
+      </c>
+      <c r="M57" s="1">
+        <v>0</v>
+      </c>
+      <c r="N57" s="1">
+        <v>0</v>
+      </c>
+      <c r="O57" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P57" s="1">
+        <v>2521</v>
+      </c>
+      <c r="Q57" s="1">
+        <v>2081</v>
+      </c>
+      <c r="R57" s="1">
+        <v>4.18</v>
+      </c>
+      <c r="S57" s="1">
+        <v>2959</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>134</v>
+      </c>
+      <c r="B58" t="s">
+        <v>135</v>
+      </c>
+      <c r="C58" s="1">
+        <v>24</v>
+      </c>
+      <c r="D58" s="1">
+        <v>8</v>
+      </c>
+      <c r="E58" s="1">
+        <v>30</v>
+      </c>
+      <c r="F58" s="1">
+        <v>62</v>
+      </c>
+      <c r="G58" s="1">
+        <v>0</v>
+      </c>
+      <c r="H58" s="1">
+        <v>0</v>
+      </c>
+      <c r="I58" s="1">
+        <v>0</v>
+      </c>
+      <c r="J58" s="1">
+        <v>0</v>
+      </c>
+      <c r="K58" s="1">
+        <v>0</v>
+      </c>
+      <c r="L58" s="1">
+        <v>0</v>
+      </c>
+      <c r="M58" s="1">
+        <v>0</v>
+      </c>
+      <c r="N58" s="1">
+        <v>0</v>
+      </c>
+      <c r="O58" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P58" s="1">
+        <v>2688</v>
+      </c>
+      <c r="Q58" s="1">
+        <v>1796</v>
+      </c>
+      <c r="R58" s="1">
+        <v>4.32</v>
+      </c>
+      <c r="S58" s="1">
+        <v>3336</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>132</v>
+      </c>
+      <c r="B59" t="s">
+        <v>133</v>
+      </c>
+      <c r="C59" s="1">
+        <v>10</v>
+      </c>
+      <c r="D59" s="1">
+        <v>14</v>
+      </c>
+      <c r="E59" s="1">
+        <v>51</v>
+      </c>
+      <c r="F59" s="1">
+        <v>36</v>
+      </c>
+      <c r="G59" s="1">
+        <v>0</v>
+      </c>
+      <c r="H59" s="1">
+        <v>0</v>
+      </c>
+      <c r="I59" s="1">
+        <v>0</v>
+      </c>
+      <c r="J59" s="1">
+        <v>0</v>
+      </c>
+      <c r="K59" s="1">
+        <v>0</v>
+      </c>
+      <c r="L59" s="1">
+        <v>0</v>
+      </c>
+      <c r="M59" s="1">
+        <v>0</v>
+      </c>
+      <c r="N59" s="1">
+        <v>0</v>
+      </c>
+      <c r="O59" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P59" s="1">
+        <v>2694</v>
+      </c>
+      <c r="Q59" s="1">
+        <v>1726</v>
+      </c>
+      <c r="R59" s="1">
+        <v>3.44</v>
+      </c>
+      <c r="S59" s="1">
+        <v>2688</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>141</v>
+      </c>
+      <c r="B60" t="s">
+        <v>142</v>
+      </c>
+      <c r="C60" s="1">
+        <v>23</v>
+      </c>
+      <c r="D60" s="1">
+        <v>15</v>
+      </c>
+      <c r="E60" s="1">
+        <v>6</v>
+      </c>
+      <c r="F60" s="1">
+        <v>79</v>
+      </c>
+      <c r="G60" s="1">
+        <v>0</v>
+      </c>
+      <c r="H60" s="1">
+        <v>0</v>
+      </c>
+      <c r="I60" s="1">
+        <v>0</v>
+      </c>
+      <c r="J60" s="1">
+        <v>0</v>
+      </c>
+      <c r="K60" s="1">
+        <v>0</v>
+      </c>
+      <c r="L60" s="1">
+        <v>0</v>
+      </c>
+      <c r="M60" s="1">
+        <v>0</v>
+      </c>
+      <c r="N60" s="1">
+        <v>0</v>
+      </c>
+      <c r="O60" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P60" s="1">
+        <v>2822</v>
+      </c>
+      <c r="Q60" s="1">
+        <v>1534</v>
+      </c>
+      <c r="R60" s="1">
+        <v>6.09</v>
+      </c>
+      <c r="S60" s="1">
+        <v>3345</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>143</v>
+      </c>
+      <c r="B61" t="s">
+        <v>144</v>
+      </c>
+      <c r="C61" s="1">
+        <v>11</v>
+      </c>
+      <c r="D61" s="1">
+        <v>2</v>
+      </c>
+      <c r="E61" s="1">
+        <v>39</v>
+      </c>
+      <c r="F61" s="1">
+        <v>59</v>
+      </c>
+      <c r="G61" s="1">
+        <v>0</v>
+      </c>
+      <c r="H61" s="1">
+        <v>0</v>
+      </c>
+      <c r="I61" s="1">
+        <v>0</v>
+      </c>
+      <c r="J61" s="1">
+        <v>0</v>
+      </c>
+      <c r="K61" s="1">
+        <v>0</v>
+      </c>
+      <c r="L61" s="1">
+        <v>0</v>
+      </c>
+      <c r="M61" s="1">
+        <v>0</v>
+      </c>
+      <c r="N61" s="1">
+        <v>0</v>
+      </c>
+      <c r="O61" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P61" s="1">
+        <v>2942</v>
+      </c>
+      <c r="Q61" s="1">
+        <v>2287</v>
+      </c>
+      <c r="R61" s="1">
+        <v>4.51</v>
+      </c>
+      <c r="S61" s="1">
+        <v>3554</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>149</v>
+      </c>
+      <c r="B62" t="s">
+        <v>150</v>
+      </c>
+      <c r="C62" s="1">
+        <v>20</v>
+      </c>
+      <c r="D62" s="1">
+        <v>9</v>
+      </c>
+      <c r="E62" s="1">
+        <v>9</v>
+      </c>
+      <c r="F62" s="1">
+        <v>82</v>
+      </c>
+      <c r="G62" s="1">
+        <v>0</v>
+      </c>
+      <c r="H62" s="1">
+        <v>0</v>
+      </c>
+      <c r="I62" s="1">
+        <v>0</v>
+      </c>
+      <c r="J62" s="1">
+        <v>0</v>
+      </c>
+      <c r="K62" s="1">
+        <v>0</v>
+      </c>
+      <c r="L62" s="1">
+        <v>0</v>
+      </c>
+      <c r="M62" s="1">
+        <v>0</v>
+      </c>
+      <c r="N62" s="1">
+        <v>0</v>
+      </c>
+      <c r="O62" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P62" s="1">
+        <v>2973</v>
+      </c>
+      <c r="Q62" s="1">
+        <v>1961</v>
+      </c>
+      <c r="R62" s="1">
+        <v>6.63</v>
+      </c>
+      <c r="S62" s="1">
+        <v>3490</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>147</v>
+      </c>
+      <c r="B63" t="s">
+        <v>148</v>
+      </c>
+      <c r="C63" s="1">
+        <v>12</v>
+      </c>
+      <c r="D63" s="1">
+        <v>13</v>
+      </c>
+      <c r="E63" s="1">
+        <v>6</v>
+      </c>
+      <c r="F63" s="1">
+        <v>81</v>
+      </c>
+      <c r="G63" s="1">
+        <v>0</v>
+      </c>
+      <c r="H63" s="1">
+        <v>0</v>
+      </c>
+      <c r="I63" s="1">
+        <v>0</v>
+      </c>
+      <c r="J63" s="1">
+        <v>0</v>
+      </c>
+      <c r="K63" s="1">
+        <v>0</v>
+      </c>
+      <c r="L63" s="1">
+        <v>0</v>
+      </c>
+      <c r="M63" s="1">
+        <v>0</v>
+      </c>
+      <c r="N63" s="1">
+        <v>0</v>
+      </c>
+      <c r="O63" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P63" s="1">
+        <v>3025</v>
+      </c>
+      <c r="Q63" s="1">
+        <v>1941</v>
+      </c>
+      <c r="R63" s="1">
+        <v>6.41</v>
+      </c>
+      <c r="S63" s="1">
+        <v>3503</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>136</v>
+      </c>
+      <c r="B64" t="s">
+        <v>137</v>
+      </c>
+      <c r="C64" s="1">
+        <v>47</v>
+      </c>
+      <c r="D64" s="1">
+        <v>22</v>
+      </c>
+      <c r="E64" s="1">
+        <v>29</v>
+      </c>
+      <c r="F64" s="1">
+        <v>24</v>
+      </c>
+      <c r="G64" s="1">
+        <v>25</v>
+      </c>
+      <c r="H64" s="1">
+        <v>0</v>
+      </c>
+      <c r="I64" s="1">
+        <v>0</v>
+      </c>
+      <c r="J64" s="1">
+        <v>0</v>
+      </c>
+      <c r="K64" s="1">
+        <v>0</v>
+      </c>
+      <c r="L64" s="1">
+        <v>0</v>
+      </c>
+      <c r="M64" s="1">
+        <v>0</v>
+      </c>
+      <c r="N64" s="1">
+        <v>0</v>
+      </c>
+      <c r="O64" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="P64" s="1">
+        <v>3063</v>
+      </c>
+      <c r="Q64" s="1">
+        <v>1340</v>
+      </c>
+      <c r="R64" s="1">
+        <v>1.78</v>
+      </c>
+      <c r="S64" s="1">
+        <v>2534</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>139</v>
+      </c>
+      <c r="B65" t="s">
+        <v>140</v>
+      </c>
+      <c r="C65" s="1">
+        <v>14</v>
+      </c>
+      <c r="D65" s="1">
+        <v>23</v>
+      </c>
+      <c r="E65" s="1">
+        <v>23</v>
+      </c>
+      <c r="F65" s="1">
+        <v>54</v>
+      </c>
+      <c r="G65" s="1">
+        <v>0</v>
+      </c>
+      <c r="H65" s="1">
+        <v>0</v>
+      </c>
+      <c r="I65" s="1">
+        <v>0</v>
+      </c>
+      <c r="J65" s="1">
+        <v>0</v>
+      </c>
+      <c r="K65" s="1">
+        <v>0</v>
+      </c>
+      <c r="L65" s="1">
+        <v>0</v>
+      </c>
+      <c r="M65" s="1">
+        <v>0</v>
+      </c>
+      <c r="N65" s="1">
+        <v>0</v>
+      </c>
+      <c r="O65" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P65" s="1">
+        <v>3066</v>
+      </c>
+      <c r="Q65" s="1">
+        <v>1552</v>
+      </c>
+      <c r="R65" s="1">
+        <v>3.36</v>
+      </c>
+      <c r="S65" s="1">
+        <v>3674</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>124</v>
+      </c>
+      <c r="B66" t="s">
+        <v>125</v>
+      </c>
+      <c r="C66" s="1">
+        <v>92</v>
+      </c>
+      <c r="D66" s="1">
+        <v>52</v>
+      </c>
+      <c r="E66" s="1">
+        <v>13</v>
+      </c>
+      <c r="F66" s="1">
+        <v>13</v>
+      </c>
+      <c r="G66" s="1">
+        <v>0</v>
+      </c>
+      <c r="H66" s="1">
+        <v>21</v>
+      </c>
+      <c r="I66" s="1">
+        <v>0</v>
+      </c>
+      <c r="J66" s="1">
+        <v>0</v>
+      </c>
+      <c r="K66" s="1">
+        <v>0</v>
+      </c>
+      <c r="L66" s="1">
+        <v>0</v>
+      </c>
+      <c r="M66" s="1">
+        <v>0</v>
+      </c>
+      <c r="N66" s="1">
+        <v>0</v>
+      </c>
+      <c r="O66" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P66" s="1">
+        <v>3152</v>
+      </c>
+      <c r="Q66" s="1">
+        <v>1097</v>
+      </c>
+      <c r="R66" s="1">
+        <v>2.88</v>
+      </c>
+      <c r="S66" s="1">
+        <v>1436</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>126</v>
+      </c>
+      <c r="B67" t="s">
+        <v>127</v>
+      </c>
+      <c r="C67" s="1">
+        <v>51</v>
+      </c>
+      <c r="D67" s="1">
+        <v>50</v>
+      </c>
+      <c r="E67" s="1">
+        <v>13</v>
+      </c>
+      <c r="F67" s="1">
+        <v>0</v>
+      </c>
+      <c r="G67" s="1">
+        <v>36</v>
+      </c>
+      <c r="H67" s="1">
+        <v>0</v>
+      </c>
+      <c r="I67" s="1">
+        <v>0</v>
+      </c>
+      <c r="J67" s="1">
+        <v>0</v>
+      </c>
+      <c r="K67" s="1">
+        <v>0</v>
+      </c>
+      <c r="L67" s="1">
+        <v>0</v>
+      </c>
+      <c r="M67" s="1">
+        <v>0</v>
+      </c>
+      <c r="N67" s="1">
+        <v>0</v>
+      </c>
+      <c r="O67" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P67" s="1">
+        <v>3169</v>
+      </c>
+      <c r="Q67" s="1">
+        <v>862</v>
+      </c>
+      <c r="R67" s="1">
+        <v>3.45</v>
+      </c>
+      <c r="S67" s="1">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>130</v>
+      </c>
+      <c r="B68" t="s">
+        <v>131</v>
+      </c>
+      <c r="C68" s="1">
+        <v>50</v>
+      </c>
+      <c r="D68" s="1">
+        <v>54</v>
+      </c>
+      <c r="E68" s="1">
+        <v>7</v>
+      </c>
+      <c r="F68" s="1">
+        <v>0</v>
+      </c>
+      <c r="G68" s="1">
+        <v>39</v>
+      </c>
+      <c r="H68" s="1">
+        <v>0</v>
+      </c>
+      <c r="I68" s="1">
+        <v>0</v>
+      </c>
+      <c r="J68" s="1">
+        <v>0</v>
+      </c>
+      <c r="K68" s="1">
+        <v>0</v>
+      </c>
+      <c r="L68" s="1">
+        <v>0</v>
+      </c>
+      <c r="M68" s="1">
+        <v>0</v>
+      </c>
+      <c r="N68" s="1">
+        <v>0</v>
+      </c>
+      <c r="O68" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P68" s="1">
+        <v>3268</v>
+      </c>
+      <c r="Q68" s="1">
+        <v>964</v>
+      </c>
+      <c r="R68" s="1">
+        <v>3.95</v>
+      </c>
+      <c r="S68" s="1">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>157</v>
+      </c>
+      <c r="B69" t="s">
+        <v>158</v>
+      </c>
+      <c r="C69" s="1">
+        <v>19</v>
+      </c>
+      <c r="D69" s="1">
+        <v>2</v>
+      </c>
+      <c r="E69" s="1">
+        <v>2</v>
+      </c>
+      <c r="F69" s="1">
+        <v>96</v>
+      </c>
+      <c r="G69" s="1">
+        <v>0</v>
+      </c>
+      <c r="H69" s="1">
+        <v>0</v>
+      </c>
+      <c r="I69" s="1">
+        <v>0</v>
+      </c>
+      <c r="J69" s="1">
+        <v>0</v>
+      </c>
+      <c r="K69" s="1">
+        <v>0</v>
+      </c>
+      <c r="L69" s="1">
+        <v>0</v>
+      </c>
+      <c r="M69" s="1">
+        <v>0</v>
+      </c>
+      <c r="N69" s="1">
+        <v>0</v>
+      </c>
+      <c r="O69" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P69" s="1">
+        <v>3280</v>
+      </c>
+      <c r="Q69" s="1">
+        <v>2771</v>
+      </c>
+      <c r="R69" s="1">
+        <v>9.2100000000000009</v>
+      </c>
+      <c r="S69" s="1">
+        <v>3520</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>151</v>
+      </c>
+      <c r="B70" t="s">
+        <v>152</v>
+      </c>
+      <c r="C70" s="1">
+        <v>66</v>
+      </c>
+      <c r="D70" s="1">
+        <v>29</v>
+      </c>
+      <c r="E70" s="1">
+        <v>31</v>
+      </c>
+      <c r="F70" s="1">
+        <v>0</v>
+      </c>
+      <c r="G70" s="1">
+        <v>40</v>
+      </c>
+      <c r="H70" s="1">
+        <v>0</v>
+      </c>
+      <c r="I70" s="1">
+        <v>0</v>
+      </c>
+      <c r="J70" s="1">
+        <v>0</v>
+      </c>
+      <c r="K70" s="1">
+        <v>0</v>
+      </c>
+      <c r="L70" s="1">
+        <v>0</v>
+      </c>
+      <c r="M70" s="1">
+        <v>0</v>
+      </c>
+      <c r="N70" s="1">
+        <v>0</v>
+      </c>
+      <c r="O70" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P70" s="1">
+        <v>3710</v>
+      </c>
+      <c r="Q70" s="1">
+        <v>1301</v>
+      </c>
+      <c r="R70" s="1">
+        <v>2.75</v>
+      </c>
+      <c r="S70" s="1">
+        <v>2094</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>155</v>
+      </c>
+      <c r="B71" t="s">
+        <v>156</v>
+      </c>
+      <c r="C71" s="1">
+        <v>24</v>
+      </c>
+      <c r="D71" s="1">
+        <v>19</v>
+      </c>
+      <c r="E71" s="1">
+        <v>26</v>
+      </c>
+      <c r="F71" s="1">
+        <v>13</v>
+      </c>
+      <c r="G71" s="1">
+        <v>42</v>
+      </c>
+      <c r="H71" s="1">
+        <v>0</v>
+      </c>
+      <c r="I71" s="1">
+        <v>0</v>
+      </c>
+      <c r="J71" s="1">
+        <v>0</v>
+      </c>
+      <c r="K71" s="1">
+        <v>0</v>
+      </c>
+      <c r="L71" s="1">
+        <v>0</v>
+      </c>
+      <c r="M71" s="1">
+        <v>0</v>
+      </c>
+      <c r="N71" s="1">
+        <v>0</v>
+      </c>
+      <c r="O71" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P71" s="1">
+        <v>3841</v>
+      </c>
+      <c r="Q71" s="1">
+        <v>1421</v>
+      </c>
+      <c r="R71" s="1">
+        <v>2.25</v>
+      </c>
+      <c r="S71" s="1">
+        <v>1864</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>145</v>
+      </c>
+      <c r="B72" t="s">
+        <v>146</v>
+      </c>
+      <c r="C72" s="1">
+        <v>177</v>
+      </c>
+      <c r="D72" s="1">
+        <v>24</v>
+      </c>
+      <c r="E72" s="1">
+        <v>36</v>
+      </c>
+      <c r="F72" s="1">
+        <v>18</v>
+      </c>
+      <c r="G72" s="1">
+        <v>7</v>
+      </c>
+      <c r="H72" s="1">
+        <v>14</v>
+      </c>
+      <c r="I72" s="1">
+        <v>0</v>
+      </c>
+      <c r="J72" s="1">
+        <v>0</v>
+      </c>
+      <c r="K72" s="1">
+        <v>0</v>
+      </c>
+      <c r="L72" s="1">
+        <v>0</v>
+      </c>
+      <c r="M72" s="1">
+        <v>0</v>
+      </c>
+      <c r="N72" s="1">
+        <v>0</v>
+      </c>
+      <c r="O72" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="P72" s="1">
+        <v>3916</v>
+      </c>
+      <c r="Q72" s="1">
+        <v>1451</v>
+      </c>
+      <c r="R72" s="1">
+        <v>1.71</v>
+      </c>
+      <c r="S72" s="1">
+        <v>2153</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>159</v>
+      </c>
+      <c r="B73" t="s">
+        <v>160</v>
+      </c>
+      <c r="C73" s="1">
+        <v>152</v>
+      </c>
+      <c r="D73" s="1">
+        <v>35</v>
+      </c>
+      <c r="E73" s="1">
+        <v>10</v>
+      </c>
+      <c r="F73" s="1">
+        <v>11</v>
+      </c>
+      <c r="G73" s="1">
+        <v>35</v>
+      </c>
+      <c r="H73" s="1">
+        <v>9</v>
+      </c>
+      <c r="I73" s="1">
+        <v>0</v>
+      </c>
+      <c r="J73" s="1">
+        <v>0</v>
+      </c>
+      <c r="K73" s="1">
+        <v>0</v>
+      </c>
+      <c r="L73" s="1">
+        <v>0</v>
+      </c>
+      <c r="M73" s="1">
+        <v>0</v>
+      </c>
+      <c r="N73" s="1">
+        <v>0</v>
+      </c>
+      <c r="O73" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P73" s="1">
+        <v>4195</v>
+      </c>
+      <c r="Q73" s="1">
+        <v>1211</v>
+      </c>
+      <c r="R73" s="1">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="S73" s="1">
+        <v>1712</v>
+      </c>
+    </row>
+    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>153</v>
+      </c>
+      <c r="B74" t="s">
+        <v>154</v>
+      </c>
+      <c r="C74" s="1">
+        <v>126</v>
+      </c>
+      <c r="D74" s="1">
+        <v>26</v>
+      </c>
+      <c r="E74" s="1">
+        <v>26</v>
+      </c>
+      <c r="F74" s="1">
+        <v>19</v>
+      </c>
+      <c r="G74" s="1">
+        <v>20</v>
+      </c>
+      <c r="H74" s="1">
+        <v>10</v>
+      </c>
+      <c r="I74" s="1">
+        <v>0</v>
+      </c>
+      <c r="J74" s="1">
+        <v>0</v>
+      </c>
+      <c r="K74" s="1">
+        <v>0</v>
+      </c>
+      <c r="L74" s="1">
+        <v>0</v>
+      </c>
+      <c r="M74" s="1">
+        <v>0</v>
+      </c>
+      <c r="N74" s="1">
+        <v>0</v>
+      </c>
+      <c r="O74" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="P74" s="1">
+        <v>4236</v>
+      </c>
+      <c r="Q74" s="1">
+        <v>1377</v>
+      </c>
+      <c r="R74" s="1">
+        <v>1.4</v>
+      </c>
+      <c r="S74" s="1">
+        <v>2303</v>
+      </c>
+    </row>
+    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>167</v>
+      </c>
+      <c r="B75" t="s">
+        <v>168</v>
+      </c>
+      <c r="C75" s="1">
+        <v>88</v>
+      </c>
+      <c r="D75" s="1">
+        <v>18</v>
+      </c>
+      <c r="E75" s="1">
+        <v>24</v>
+      </c>
+      <c r="F75" s="1">
+        <v>7</v>
+      </c>
+      <c r="G75" s="1">
+        <v>42</v>
+      </c>
+      <c r="H75" s="1">
+        <v>10</v>
+      </c>
+      <c r="I75" s="1">
+        <v>0</v>
+      </c>
+      <c r="J75" s="1">
+        <v>0</v>
+      </c>
+      <c r="K75" s="1">
+        <v>0</v>
+      </c>
+      <c r="L75" s="1">
+        <v>0</v>
+      </c>
+      <c r="M75" s="1">
+        <v>0</v>
+      </c>
+      <c r="N75" s="1">
+        <v>0</v>
+      </c>
+      <c r="O75" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P75" s="1">
+        <v>4551</v>
+      </c>
+      <c r="Q75" s="1">
+        <v>1580</v>
+      </c>
+      <c r="R75" s="1">
+        <v>2.04</v>
+      </c>
+      <c r="S75" s="1">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>171</v>
+      </c>
+      <c r="B76" t="s">
+        <v>172</v>
+      </c>
+      <c r="C76" s="1">
+        <v>75</v>
+      </c>
+      <c r="D76" s="1">
+        <v>18</v>
+      </c>
+      <c r="E76" s="1">
+        <v>18</v>
+      </c>
+      <c r="F76" s="1">
+        <v>7</v>
+      </c>
+      <c r="G76" s="1">
+        <v>46</v>
+      </c>
+      <c r="H76" s="1">
+        <v>11</v>
+      </c>
+      <c r="I76" s="1">
+        <v>0</v>
+      </c>
+      <c r="J76" s="1">
+        <v>0</v>
+      </c>
+      <c r="K76" s="1">
+        <v>0</v>
+      </c>
+      <c r="L76" s="1">
+        <v>0</v>
+      </c>
+      <c r="M76" s="1">
+        <v>0</v>
+      </c>
+      <c r="N76" s="1">
+        <v>0</v>
+      </c>
+      <c r="O76" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P76" s="1">
+        <v>4797</v>
+      </c>
+      <c r="Q76" s="1">
+        <v>1591</v>
+      </c>
+      <c r="R76" s="1">
+        <v>2.21</v>
+      </c>
+      <c r="S76" s="1">
+        <v>2562</v>
+      </c>
+    </row>
+    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>163</v>
+      </c>
+      <c r="B77" t="s">
+        <v>164</v>
+      </c>
+      <c r="C77" s="1">
+        <v>46</v>
+      </c>
+      <c r="D77" s="1">
+        <v>12</v>
+      </c>
+      <c r="E77" s="1">
+        <v>32</v>
+      </c>
+      <c r="F77" s="1">
+        <v>18</v>
+      </c>
+      <c r="G77" s="1">
+        <v>19</v>
+      </c>
+      <c r="H77" s="1">
+        <v>19</v>
+      </c>
+      <c r="I77" s="1">
+        <v>0</v>
+      </c>
+      <c r="J77" s="1">
+        <v>0</v>
+      </c>
+      <c r="K77" s="1">
+        <v>0</v>
+      </c>
+      <c r="L77" s="1">
+        <v>0</v>
+      </c>
+      <c r="M77" s="1">
+        <v>0</v>
+      </c>
+      <c r="N77" s="1">
+        <v>0</v>
+      </c>
+      <c r="O77" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="P77" s="1">
+        <v>4812</v>
+      </c>
+      <c r="Q77" s="1">
+        <v>2053</v>
+      </c>
+      <c r="R77" s="1">
+        <v>1.44</v>
+      </c>
+      <c r="S77" s="1">
+        <v>2952</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>161</v>
+      </c>
+      <c r="B78" t="s">
+        <v>162</v>
+      </c>
+      <c r="C78" s="1">
+        <v>26</v>
+      </c>
+      <c r="D78" s="1">
+        <v>6</v>
+      </c>
+      <c r="E78" s="1">
+        <v>52</v>
+      </c>
+      <c r="F78" s="1">
+        <v>10</v>
+      </c>
+      <c r="G78" s="1">
+        <v>0</v>
+      </c>
+      <c r="H78" s="1">
+        <v>32</v>
+      </c>
+      <c r="I78" s="1">
+        <v>0</v>
+      </c>
+      <c r="J78" s="1">
+        <v>0</v>
+      </c>
+      <c r="K78" s="1">
+        <v>0</v>
+      </c>
+      <c r="L78" s="1">
+        <v>0</v>
+      </c>
+      <c r="M78" s="1">
+        <v>0</v>
+      </c>
+      <c r="N78" s="1">
+        <v>0</v>
+      </c>
+      <c r="O78" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P78" s="1">
+        <v>4943</v>
+      </c>
+      <c r="Q78" s="1">
+        <v>2122</v>
+      </c>
+      <c r="R78" s="1">
+        <v>3.26</v>
+      </c>
+      <c r="S78" s="1">
+        <v>2234</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>178</v>
+      </c>
+      <c r="B79" t="s">
+        <v>179</v>
+      </c>
+      <c r="C79" s="1">
+        <v>46</v>
+      </c>
+      <c r="D79" s="1">
+        <v>4</v>
+      </c>
+      <c r="E79" s="1">
+        <v>15</v>
+      </c>
+      <c r="F79" s="1">
+        <v>39</v>
+      </c>
+      <c r="G79" s="1">
+        <v>21</v>
+      </c>
+      <c r="H79" s="1">
+        <v>21</v>
+      </c>
+      <c r="I79" s="1">
+        <v>0</v>
+      </c>
+      <c r="J79" s="1">
+        <v>0</v>
+      </c>
+      <c r="K79" s="1">
+        <v>0</v>
+      </c>
+      <c r="L79" s="1">
+        <v>0</v>
+      </c>
+      <c r="M79" s="1">
+        <v>0</v>
+      </c>
+      <c r="N79" s="1">
+        <v>0</v>
+      </c>
+      <c r="O79" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="P79" s="1">
+        <v>5181</v>
+      </c>
+      <c r="Q79" s="1">
+        <v>2494</v>
+      </c>
+      <c r="R79" s="1">
+        <v>1.91</v>
+      </c>
+      <c r="S79" s="1">
+        <v>4506</v>
+      </c>
+    </row>
+    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>165</v>
+      </c>
+      <c r="B80" t="s">
+        <v>166</v>
+      </c>
+      <c r="C80" s="1">
+        <v>31</v>
+      </c>
+      <c r="D80" s="1">
+        <v>25</v>
+      </c>
+      <c r="E80" s="1">
+        <v>16</v>
+      </c>
+      <c r="F80" s="1">
+        <v>23</v>
+      </c>
+      <c r="G80" s="1">
+        <v>0</v>
+      </c>
+      <c r="H80" s="1">
+        <v>36</v>
+      </c>
+      <c r="I80" s="1">
+        <v>0</v>
+      </c>
+      <c r="J80" s="1">
+        <v>0</v>
+      </c>
+      <c r="K80" s="1">
+        <v>0</v>
+      </c>
+      <c r="L80" s="1">
+        <v>0</v>
+      </c>
+      <c r="M80" s="1">
+        <v>0</v>
+      </c>
+      <c r="N80" s="1">
+        <v>0</v>
+      </c>
+      <c r="O80" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="P80" s="1">
+        <v>5361</v>
+      </c>
+      <c r="Q80" s="1">
+        <v>1134</v>
+      </c>
+      <c r="R80" s="1">
+        <v>1.97</v>
+      </c>
+      <c r="S80" s="1">
+        <v>2509</v>
+      </c>
+    </row>
+    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>173</v>
+      </c>
+      <c r="B81" t="s">
+        <v>174</v>
+      </c>
+      <c r="C81" s="1">
+        <v>28</v>
+      </c>
+      <c r="D81" s="1">
+        <v>8</v>
+      </c>
+      <c r="E81" s="1">
+        <v>9</v>
+      </c>
+      <c r="F81" s="1">
+        <v>43</v>
+      </c>
+      <c r="G81" s="1">
+        <v>20</v>
+      </c>
+      <c r="H81" s="1">
+        <v>20</v>
+      </c>
+      <c r="I81" s="1">
+        <v>0</v>
+      </c>
+      <c r="J81" s="1">
+        <v>0</v>
+      </c>
+      <c r="K81" s="1">
+        <v>0</v>
+      </c>
+      <c r="L81" s="1">
+        <v>0</v>
+      </c>
+      <c r="M81" s="1">
+        <v>0</v>
+      </c>
+      <c r="N81" s="1">
+        <v>0</v>
+      </c>
+      <c r="O81" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P81" s="1">
+        <v>5391</v>
+      </c>
+      <c r="Q81" s="1">
+        <v>2200</v>
+      </c>
+      <c r="R81" s="1">
+        <v>2.09</v>
+      </c>
+      <c r="S81" s="1">
+        <v>3530</v>
+      </c>
+    </row>
+    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>184</v>
+      </c>
+      <c r="B82" t="s">
+        <v>185</v>
+      </c>
+      <c r="C82" s="1">
+        <v>25</v>
+      </c>
+      <c r="D82" s="1">
+        <v>9</v>
+      </c>
+      <c r="E82" s="1">
+        <v>8</v>
+      </c>
+      <c r="F82" s="1">
+        <v>20</v>
+      </c>
+      <c r="G82" s="1">
+        <v>42</v>
+      </c>
+      <c r="H82" s="1">
+        <v>21</v>
+      </c>
+      <c r="I82" s="1">
+        <v>0</v>
+      </c>
+      <c r="J82" s="1">
+        <v>0</v>
+      </c>
+      <c r="K82" s="1">
+        <v>0</v>
+      </c>
+      <c r="L82" s="1">
+        <v>0</v>
+      </c>
+      <c r="M82" s="1">
+        <v>0</v>
+      </c>
+      <c r="N82" s="1">
+        <v>0</v>
+      </c>
+      <c r="O82" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P82" s="1">
+        <v>5614</v>
+      </c>
+      <c r="Q82" s="1">
+        <v>2704</v>
+      </c>
+      <c r="R82" s="1">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="S82" s="1">
+        <v>5277</v>
+      </c>
+    </row>
+    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>188</v>
+      </c>
+      <c r="B83" t="s">
+        <v>189</v>
+      </c>
+      <c r="C83" s="1">
+        <v>44</v>
+      </c>
+      <c r="D83" s="1">
+        <v>8</v>
+      </c>
+      <c r="E83" s="1">
+        <v>20</v>
+      </c>
+      <c r="F83" s="1">
+        <v>8</v>
+      </c>
+      <c r="G83" s="1">
+        <v>26</v>
+      </c>
+      <c r="H83" s="1">
+        <v>39</v>
+      </c>
+      <c r="I83" s="1">
+        <v>0</v>
+      </c>
+      <c r="J83" s="1">
+        <v>0</v>
+      </c>
+      <c r="K83" s="1">
+        <v>0</v>
+      </c>
+      <c r="L83" s="1">
+        <v>0</v>
+      </c>
+      <c r="M83" s="1">
+        <v>0</v>
+      </c>
+      <c r="N83" s="1">
+        <v>0</v>
+      </c>
+      <c r="O83" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="P83" s="1">
+        <v>6204</v>
+      </c>
+      <c r="Q83" s="1">
+        <v>2277</v>
+      </c>
+      <c r="R83" s="1">
+        <v>1.94</v>
+      </c>
+      <c r="S83" s="1">
+        <v>5479</v>
+      </c>
+    </row>
+    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>169</v>
+      </c>
+      <c r="B84" t="s">
+        <v>170</v>
+      </c>
+      <c r="C84" s="1">
+        <v>43</v>
+      </c>
+      <c r="D84" s="1">
+        <v>21</v>
+      </c>
+      <c r="E84" s="1">
+        <v>23</v>
+      </c>
+      <c r="F84" s="1">
+        <v>32</v>
+      </c>
+      <c r="G84" s="1">
+        <v>0</v>
+      </c>
+      <c r="H84" s="1">
+        <v>25</v>
+      </c>
+      <c r="I84" s="1">
+        <v>0</v>
+      </c>
+      <c r="J84" s="1">
+        <v>0</v>
+      </c>
+      <c r="K84" s="1">
+        <v>0</v>
+      </c>
+      <c r="L84" s="1">
+        <v>0</v>
+      </c>
+      <c r="M84" s="1">
+        <v>0</v>
+      </c>
+      <c r="N84" s="1">
+        <v>0</v>
+      </c>
+      <c r="O84" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="P84" s="1">
+        <v>6238</v>
+      </c>
+      <c r="Q84" s="1">
+        <v>1990</v>
+      </c>
+      <c r="R84" s="1">
+        <v>1.82</v>
+      </c>
+      <c r="S84" s="1">
+        <v>3394</v>
+      </c>
+    </row>
+    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>182</v>
+      </c>
+      <c r="B85" t="s">
+        <v>183</v>
+      </c>
+      <c r="C85" s="1">
+        <v>336</v>
+      </c>
+      <c r="D85" s="1">
+        <v>13</v>
+      </c>
+      <c r="E85" s="1">
+        <v>18</v>
+      </c>
+      <c r="F85" s="1">
+        <v>16</v>
+      </c>
+      <c r="G85" s="1">
+        <v>31</v>
+      </c>
+      <c r="H85" s="1">
+        <v>13</v>
+      </c>
+      <c r="I85" s="1">
+        <v>10</v>
+      </c>
+      <c r="J85" s="1">
+        <v>0</v>
+      </c>
+      <c r="K85" s="1">
+        <v>0</v>
+      </c>
+      <c r="L85" s="1">
+        <v>0</v>
+      </c>
+      <c r="M85" s="1">
+        <v>0</v>
+      </c>
+      <c r="N85" s="1">
+        <v>0</v>
+      </c>
+      <c r="O85" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="P85" s="1">
+        <v>6471</v>
+      </c>
+      <c r="Q85" s="1">
+        <v>1919</v>
+      </c>
+      <c r="R85" s="1">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="S85" s="1">
+        <v>3660</v>
+      </c>
+    </row>
+    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>192</v>
+      </c>
+      <c r="B86" t="s">
+        <v>193</v>
+      </c>
+      <c r="C86" s="1">
+        <v>10</v>
+      </c>
+      <c r="D86" s="1">
+        <v>18</v>
+      </c>
+      <c r="E86" s="1">
+        <v>7</v>
+      </c>
+      <c r="F86" s="1">
+        <v>0</v>
+      </c>
+      <c r="G86" s="1">
+        <v>75</v>
+      </c>
+      <c r="H86" s="1">
+        <v>0</v>
+      </c>
+      <c r="I86" s="1">
+        <v>0</v>
+      </c>
+      <c r="J86" s="1">
+        <v>0</v>
+      </c>
+      <c r="K86" s="1">
+        <v>0</v>
+      </c>
+      <c r="L86" s="1">
+        <v>0</v>
+      </c>
+      <c r="M86" s="1">
+        <v>0</v>
+      </c>
+      <c r="N86" s="1">
+        <v>0</v>
+      </c>
+      <c r="O86" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P86" s="1">
+        <v>6603</v>
+      </c>
+      <c r="Q86" s="1">
+        <v>1369</v>
+      </c>
+      <c r="R86" s="1">
+        <v>5.62</v>
+      </c>
+      <c r="S86" s="1">
+        <v>2564</v>
+      </c>
+    </row>
+    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>175</v>
+      </c>
+      <c r="B87" t="s">
+        <v>176</v>
+      </c>
+      <c r="C87" s="1">
+        <v>186</v>
+      </c>
+      <c r="D87" s="1">
+        <v>21</v>
+      </c>
+      <c r="E87" s="1">
+        <v>21</v>
+      </c>
+      <c r="F87" s="1">
+        <v>10</v>
+      </c>
+      <c r="G87" s="1">
+        <v>21</v>
+      </c>
+      <c r="H87" s="1">
+        <v>16</v>
+      </c>
+      <c r="I87" s="1">
+        <v>12</v>
+      </c>
+      <c r="J87" s="1">
+        <v>0</v>
+      </c>
+      <c r="K87" s="1">
+        <v>0</v>
+      </c>
+      <c r="L87" s="1">
+        <v>0</v>
+      </c>
+      <c r="M87" s="1">
+        <v>0</v>
+      </c>
+      <c r="N87" s="1">
+        <v>0</v>
+      </c>
+      <c r="O87" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="P87" s="1">
+        <v>6642</v>
+      </c>
+      <c r="Q87" s="1">
+        <v>1618</v>
+      </c>
+      <c r="R87" s="1">
+        <v>0.97</v>
+      </c>
+      <c r="S87" s="1">
+        <v>2266</v>
+      </c>
+    </row>
+    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>186</v>
+      </c>
+      <c r="B88" t="s">
+        <v>187</v>
+      </c>
+      <c r="C88" s="1">
+        <v>15</v>
+      </c>
+      <c r="D88" s="1">
+        <v>12</v>
+      </c>
+      <c r="E88" s="1">
+        <v>22</v>
+      </c>
+      <c r="F88" s="1">
+        <v>16</v>
+      </c>
+      <c r="G88" s="1">
+        <v>0</v>
+      </c>
+      <c r="H88" s="1">
+        <v>50</v>
+      </c>
+      <c r="I88" s="1">
+        <v>0</v>
+      </c>
+      <c r="J88" s="1">
+        <v>0</v>
+      </c>
+      <c r="K88" s="1">
+        <v>0</v>
+      </c>
+      <c r="L88" s="1">
+        <v>0</v>
+      </c>
+      <c r="M88" s="1">
+        <v>0</v>
+      </c>
+      <c r="N88" s="1">
+        <v>0</v>
+      </c>
+      <c r="O88" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P88" s="1">
+        <v>7047</v>
+      </c>
+      <c r="Q88" s="1">
+        <v>2301</v>
+      </c>
+      <c r="R88" s="1">
+        <v>2.72</v>
+      </c>
+      <c r="S88" s="1">
+        <v>3060</v>
+      </c>
+    </row>
+    <row r="89" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>180</v>
+      </c>
+      <c r="B89" t="s">
+        <v>181</v>
+      </c>
+      <c r="C89" s="1">
+        <v>19</v>
+      </c>
+      <c r="D89" s="1">
+        <v>11</v>
+      </c>
+      <c r="E89" s="1">
+        <v>42</v>
+      </c>
+      <c r="F89" s="1">
+        <v>0</v>
+      </c>
+      <c r="G89" s="1">
+        <v>0</v>
+      </c>
+      <c r="H89" s="1">
+        <v>47</v>
+      </c>
+      <c r="I89" s="1">
+        <v>0</v>
+      </c>
+      <c r="J89" s="1">
+        <v>0</v>
+      </c>
+      <c r="K89" s="1">
+        <v>0</v>
+      </c>
+      <c r="L89" s="1">
+        <v>0</v>
+      </c>
+      <c r="M89" s="1">
+        <v>0</v>
+      </c>
+      <c r="N89" s="1">
+        <v>0</v>
+      </c>
+      <c r="O89" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P89" s="1">
+        <v>7489</v>
+      </c>
+      <c r="Q89" s="1">
+        <v>2164</v>
+      </c>
+      <c r="R89" s="1">
+        <v>3.48</v>
+      </c>
+      <c r="S89" s="1">
+        <v>2038</v>
+      </c>
+    </row>
+    <row r="90" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>194</v>
+      </c>
+      <c r="B90" t="s">
+        <v>195</v>
+      </c>
+      <c r="C90" s="1">
+        <v>82</v>
+      </c>
+      <c r="D90" s="1">
+        <v>11</v>
+      </c>
+      <c r="E90" s="1">
+        <v>13</v>
+      </c>
+      <c r="F90" s="1">
+        <v>23</v>
+      </c>
+      <c r="G90" s="1">
+        <v>7</v>
+      </c>
+      <c r="H90" s="1">
+        <v>15</v>
+      </c>
+      <c r="I90" s="1">
+        <v>32</v>
+      </c>
+      <c r="J90" s="1">
+        <v>0</v>
+      </c>
+      <c r="K90" s="1">
+        <v>0</v>
+      </c>
+      <c r="L90" s="1">
+        <v>0</v>
+      </c>
+      <c r="M90" s="1">
+        <v>0</v>
+      </c>
+      <c r="N90" s="1">
+        <v>0</v>
+      </c>
+      <c r="O90" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="P90" s="1">
+        <v>9486</v>
+      </c>
+      <c r="Q90" s="1">
+        <v>1988</v>
+      </c>
+      <c r="R90" s="1">
+        <v>1.29</v>
+      </c>
+      <c r="S90" s="1">
+        <v>3496</v>
+      </c>
+    </row>
+    <row r="91" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>196</v>
+      </c>
+      <c r="B91" t="s">
+        <v>197</v>
+      </c>
+      <c r="C91" s="1">
+        <v>7</v>
+      </c>
+      <c r="D91" s="1">
+        <v>6</v>
+      </c>
+      <c r="E91" s="1">
+        <v>11</v>
+      </c>
+      <c r="F91" s="1">
+        <v>20</v>
+      </c>
+      <c r="G91" s="1">
+        <v>0</v>
+      </c>
+      <c r="H91" s="1">
+        <v>63</v>
+      </c>
+      <c r="I91" s="1">
+        <v>0</v>
+      </c>
+      <c r="J91" s="1">
+        <v>0</v>
+      </c>
+      <c r="K91" s="1">
+        <v>0</v>
+      </c>
+      <c r="L91" s="1">
+        <v>0</v>
+      </c>
+      <c r="M91" s="1">
+        <v>0</v>
+      </c>
+      <c r="N91" s="1">
+        <v>0</v>
+      </c>
+      <c r="O91" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P91" s="1">
+        <v>9800</v>
+      </c>
+      <c r="Q91" s="1">
+        <v>3477</v>
+      </c>
+      <c r="R91" s="1">
+        <v>3.98</v>
+      </c>
+      <c r="S91" s="1">
+        <v>8141</v>
+      </c>
+    </row>
+    <row r="92" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>202</v>
+      </c>
+      <c r="B92" t="s">
+        <v>203</v>
+      </c>
+      <c r="C92" s="1">
+        <v>18</v>
+      </c>
+      <c r="D92" s="1">
+        <v>1</v>
+      </c>
+      <c r="E92" s="1">
+        <v>4</v>
+      </c>
+      <c r="F92" s="1">
+        <v>24</v>
+      </c>
+      <c r="G92" s="1">
+        <v>11</v>
+      </c>
+      <c r="H92" s="1">
+        <v>11</v>
+      </c>
+      <c r="I92" s="1">
+        <v>48</v>
+      </c>
+      <c r="J92" s="1">
+        <v>0</v>
+      </c>
+      <c r="K92" s="1">
+        <v>0</v>
+      </c>
+      <c r="L92" s="1">
+        <v>0</v>
+      </c>
+      <c r="M92" s="1">
+        <v>0</v>
+      </c>
+      <c r="N92" s="1">
+        <v>0</v>
+      </c>
+      <c r="O92" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P92" s="1">
+        <v>12033</v>
+      </c>
+      <c r="Q92" s="1">
+        <v>5372</v>
+      </c>
+      <c r="R92" s="1">
+        <v>2.52</v>
+      </c>
+      <c r="S92" s="1">
+        <v>12214</v>
+      </c>
+    </row>
+    <row r="93" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>198</v>
+      </c>
+      <c r="B93" t="s">
+        <v>199</v>
+      </c>
+      <c r="C93" s="1">
+        <v>123</v>
+      </c>
+      <c r="D93" s="1">
+        <v>7</v>
+      </c>
+      <c r="E93" s="1">
+        <v>18</v>
+      </c>
+      <c r="F93" s="1">
+        <v>14</v>
+      </c>
+      <c r="G93" s="1">
+        <v>17</v>
+      </c>
+      <c r="H93" s="1">
+        <v>9</v>
+      </c>
+      <c r="I93" s="1">
+        <v>9</v>
+      </c>
+      <c r="J93" s="1">
+        <v>26</v>
+      </c>
+      <c r="K93" s="1">
+        <v>0</v>
+      </c>
+      <c r="L93" s="1">
+        <v>0</v>
+      </c>
+      <c r="M93" s="1">
+        <v>0</v>
+      </c>
+      <c r="N93" s="1">
+        <v>0</v>
+      </c>
+      <c r="O93" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="P93" s="1">
+        <v>14552</v>
+      </c>
+      <c r="Q93" s="1">
+        <v>2817</v>
+      </c>
+      <c r="R93" s="1">
+        <v>0.86</v>
+      </c>
+      <c r="S93" s="1">
+        <v>4048</v>
+      </c>
+    </row>
+    <row r="94" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>206</v>
+      </c>
+      <c r="B94" t="s">
+        <v>207</v>
+      </c>
+      <c r="C94" s="1">
+        <v>31</v>
+      </c>
+      <c r="D94" s="1">
+        <v>3</v>
+      </c>
+      <c r="E94" s="1">
+        <v>12</v>
+      </c>
+      <c r="F94" s="1">
+        <v>18</v>
+      </c>
+      <c r="G94" s="1">
+        <v>22</v>
+      </c>
+      <c r="H94" s="1">
+        <v>11</v>
+      </c>
+      <c r="I94" s="1">
+        <v>0</v>
+      </c>
+      <c r="J94" s="1">
+        <v>33</v>
+      </c>
+      <c r="K94" s="1">
+        <v>0</v>
+      </c>
+      <c r="L94" s="1">
+        <v>0</v>
+      </c>
+      <c r="M94" s="1">
+        <v>0</v>
+      </c>
+      <c r="N94" s="1">
+        <v>0</v>
+      </c>
+      <c r="O94" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="P94" s="1">
+        <v>14828</v>
+      </c>
+      <c r="Q94" s="1">
+        <v>2628</v>
+      </c>
+      <c r="R94" s="1">
+        <v>1.43</v>
+      </c>
+      <c r="S94" s="1">
+        <v>7453</v>
+      </c>
+    </row>
+    <row r="95" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>208</v>
+      </c>
+      <c r="B95" t="s">
+        <v>209</v>
+      </c>
+      <c r="C95" s="1">
+        <v>57</v>
+      </c>
+      <c r="D95" s="1">
+        <v>10</v>
+      </c>
+      <c r="E95" s="1">
+        <v>7</v>
+      </c>
+      <c r="F95" s="1">
+        <v>11</v>
+      </c>
+      <c r="G95" s="1">
+        <v>9</v>
+      </c>
+      <c r="H95" s="1">
+        <v>18</v>
+      </c>
+      <c r="I95" s="1">
+        <v>19</v>
+      </c>
+      <c r="J95" s="1">
+        <v>26</v>
+      </c>
+      <c r="K95" s="1">
+        <v>0</v>
+      </c>
+      <c r="L95" s="1">
+        <v>0</v>
+      </c>
+      <c r="M95" s="1">
+        <v>0</v>
+      </c>
+      <c r="N95" s="1">
+        <v>0</v>
+      </c>
+      <c r="O95" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="P95" s="1">
+        <v>15233</v>
+      </c>
+      <c r="Q95" s="1">
+        <v>1797</v>
+      </c>
+      <c r="R95" s="1">
+        <v>0.89</v>
+      </c>
+      <c r="S95" s="1">
+        <v>4961</v>
+      </c>
+    </row>
+    <row r="96" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>200</v>
+      </c>
+      <c r="B96" t="s">
+        <v>201</v>
+      </c>
+      <c r="C96" s="1">
+        <v>45</v>
+      </c>
+      <c r="D96" s="1">
+        <v>8</v>
+      </c>
+      <c r="E96" s="1">
+        <v>16</v>
+      </c>
+      <c r="F96" s="1">
+        <v>7</v>
+      </c>
+      <c r="G96" s="1">
+        <v>23</v>
+      </c>
+      <c r="H96" s="1">
+        <v>11</v>
+      </c>
+      <c r="I96" s="1">
+        <v>0</v>
+      </c>
+      <c r="J96" s="1">
+        <v>34</v>
+      </c>
+      <c r="K96" s="1">
+        <v>0</v>
+      </c>
+      <c r="L96" s="1">
+        <v>0</v>
+      </c>
+      <c r="M96" s="1">
+        <v>0</v>
+      </c>
+      <c r="N96" s="1">
+        <v>0</v>
+      </c>
+      <c r="O96" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="P96" s="1">
+        <v>15432</v>
+      </c>
+      <c r="Q96" s="1">
+        <v>3038</v>
+      </c>
+      <c r="R96" s="1">
+        <v>1.43</v>
+      </c>
+      <c r="S96" s="1">
+        <v>3034</v>
+      </c>
+    </row>
+    <row r="97" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>190</v>
+      </c>
+      <c r="B97" t="s">
+        <v>191</v>
+      </c>
+      <c r="C97" s="1">
+        <v>78</v>
+      </c>
+      <c r="D97" s="1">
+        <v>21</v>
+      </c>
+      <c r="E97" s="1">
+        <v>15</v>
+      </c>
+      <c r="F97" s="1">
+        <v>28</v>
+      </c>
+      <c r="G97" s="1">
+        <v>0</v>
+      </c>
+      <c r="H97" s="1">
+        <v>25</v>
+      </c>
+      <c r="I97" s="1">
+        <v>0</v>
+      </c>
+      <c r="J97" s="1">
+        <v>0</v>
+      </c>
+      <c r="K97" s="1">
+        <v>0</v>
+      </c>
+      <c r="L97" s="1">
+        <v>0</v>
+      </c>
+      <c r="M97" s="1">
+        <v>11</v>
+      </c>
+      <c r="N97" s="1">
+        <v>0</v>
+      </c>
+      <c r="O97" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="P97" s="1">
+        <v>16874</v>
+      </c>
+      <c r="Q97" s="1">
+        <v>2175</v>
+      </c>
+      <c r="R97" s="1">
+        <v>1.43</v>
+      </c>
+      <c r="S97" s="1">
+        <v>2957</v>
+      </c>
+    </row>
+    <row r="98" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>204</v>
+      </c>
+      <c r="B98" t="s">
+        <v>205</v>
+      </c>
+      <c r="C98" s="1">
+        <v>42</v>
+      </c>
+      <c r="D98" s="1">
+        <v>9</v>
+      </c>
+      <c r="E98" s="1">
+        <v>13</v>
+      </c>
+      <c r="F98" s="1">
+        <v>25</v>
+      </c>
+      <c r="G98" s="1">
+        <v>0</v>
+      </c>
+      <c r="H98" s="1">
+        <v>13</v>
+      </c>
+      <c r="I98" s="1">
+        <v>0</v>
+      </c>
+      <c r="J98" s="1">
+        <v>40</v>
+      </c>
+      <c r="K98" s="1">
+        <v>0</v>
+      </c>
+      <c r="L98" s="1">
+        <v>0</v>
+      </c>
+      <c r="M98" s="1">
+        <v>0</v>
+      </c>
+      <c r="N98" s="1">
+        <v>0</v>
+      </c>
+      <c r="O98" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="P98" s="1">
+        <v>16897</v>
+      </c>
+      <c r="Q98" s="1">
+        <v>2340</v>
+      </c>
+      <c r="R98" s="1">
+        <v>1.88</v>
+      </c>
+      <c r="S98" s="1">
+        <v>3577</v>
+      </c>
+    </row>
+    <row r="99" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>210</v>
+      </c>
+      <c r="B99" t="s">
+        <v>211</v>
+      </c>
+      <c r="C99" s="1">
+        <v>54</v>
+      </c>
+      <c r="D99" s="1">
+        <v>8</v>
+      </c>
+      <c r="E99" s="1">
+        <v>11</v>
+      </c>
+      <c r="F99" s="1">
+        <v>8</v>
+      </c>
+      <c r="G99" s="1">
+        <v>18</v>
+      </c>
+      <c r="H99" s="1">
+        <v>9</v>
+      </c>
+      <c r="I99" s="1">
+        <v>19</v>
+      </c>
+      <c r="J99" s="1">
+        <v>26</v>
+      </c>
+      <c r="K99" s="1">
+        <v>0</v>
+      </c>
+      <c r="L99" s="1">
+        <v>0</v>
+      </c>
+      <c r="M99" s="1">
+        <v>0</v>
+      </c>
+      <c r="N99" s="1">
+        <v>0</v>
+      </c>
+      <c r="O99" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="P99" s="1">
+        <v>17176</v>
+      </c>
+      <c r="Q99" s="1">
+        <v>2269</v>
+      </c>
+      <c r="R99" s="1">
+        <v>0.89</v>
+      </c>
+      <c r="S99" s="1">
+        <v>3604</v>
+      </c>
+    </row>
+    <row r="100" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>218</v>
+      </c>
+      <c r="B100" t="s">
+        <v>219</v>
+      </c>
+      <c r="C100" s="1">
+        <v>186</v>
+      </c>
+      <c r="D100" s="1">
+        <v>4</v>
+      </c>
+      <c r="E100" s="1">
+        <v>9</v>
+      </c>
+      <c r="F100" s="1">
+        <v>10</v>
+      </c>
+      <c r="G100" s="1">
+        <v>14</v>
+      </c>
+      <c r="H100" s="1">
+        <v>21</v>
+      </c>
+      <c r="I100" s="1">
+        <v>19</v>
+      </c>
+      <c r="J100" s="1">
+        <v>10</v>
+      </c>
+      <c r="K100" s="1">
+        <v>14</v>
+      </c>
+      <c r="L100" s="1">
+        <v>0</v>
+      </c>
+      <c r="M100" s="1">
+        <v>0</v>
+      </c>
+      <c r="N100" s="1">
+        <v>0</v>
+      </c>
+      <c r="O100" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="P100" s="1">
+        <v>17591</v>
+      </c>
+      <c r="Q100" s="1">
+        <v>3690</v>
+      </c>
+      <c r="R100" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="S100" s="1">
+        <v>9592</v>
+      </c>
+    </row>
+    <row r="101" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>214</v>
+      </c>
+      <c r="B101" t="s">
+        <v>215</v>
+      </c>
+      <c r="C101" s="1">
+        <v>85</v>
+      </c>
+      <c r="D101" s="1">
+        <v>4</v>
+      </c>
+      <c r="E101" s="1">
+        <v>10</v>
+      </c>
+      <c r="F101" s="1">
+        <v>7</v>
+      </c>
+      <c r="G101" s="1">
+        <v>23</v>
+      </c>
+      <c r="H101" s="1">
+        <v>23</v>
+      </c>
+      <c r="I101" s="1">
+        <v>8</v>
+      </c>
+      <c r="J101" s="1">
+        <v>23</v>
+      </c>
+      <c r="K101" s="1">
+        <v>0</v>
+      </c>
+      <c r="L101" s="1">
+        <v>0</v>
+      </c>
+      <c r="M101" s="1">
+        <v>3</v>
+      </c>
+      <c r="N101" s="1">
+        <v>0</v>
+      </c>
+      <c r="O101" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="P101" s="1">
+        <v>18064</v>
+      </c>
+      <c r="Q101" s="1">
+        <v>6128</v>
+      </c>
+      <c r="R101" s="1">
+        <v>0.95</v>
+      </c>
+      <c r="S101" s="1">
+        <v>10212</v>
+      </c>
+    </row>
+    <row r="102" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>221</v>
+      </c>
+      <c r="B102" t="s">
+        <v>222</v>
+      </c>
+      <c r="C102" s="1">
+        <v>125</v>
+      </c>
+      <c r="D102" s="1">
+        <v>6</v>
+      </c>
+      <c r="E102" s="1">
+        <v>9</v>
+      </c>
+      <c r="F102" s="1">
+        <v>5</v>
+      </c>
+      <c r="G102" s="1">
+        <v>23</v>
+      </c>
+      <c r="H102" s="1">
+        <v>14</v>
+      </c>
+      <c r="I102" s="1">
+        <v>6</v>
+      </c>
+      <c r="J102" s="1">
+        <v>26</v>
+      </c>
+      <c r="K102" s="1">
+        <v>11</v>
+      </c>
+      <c r="L102" s="1">
+        <v>0</v>
+      </c>
+      <c r="M102" s="1">
+        <v>0</v>
+      </c>
+      <c r="N102" s="1">
+        <v>0</v>
+      </c>
+      <c r="O102" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="P102" s="1">
+        <v>19974</v>
+      </c>
+      <c r="Q102" s="1">
+        <v>3738</v>
+      </c>
+      <c r="R102" s="1">
+        <v>0.85</v>
+      </c>
+      <c r="S102" s="1">
+        <v>7695</v>
+      </c>
+    </row>
+    <row r="103" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>227</v>
+      </c>
+      <c r="B103" t="s">
+        <v>228</v>
+      </c>
+      <c r="C103" s="1">
+        <v>18</v>
+      </c>
+      <c r="D103" s="1">
+        <v>2</v>
+      </c>
+      <c r="E103" s="1">
+        <v>2</v>
+      </c>
+      <c r="F103" s="1">
+        <v>3</v>
+      </c>
+      <c r="G103" s="1">
+        <v>9</v>
+      </c>
+      <c r="H103" s="1">
+        <v>9</v>
+      </c>
+      <c r="I103" s="1">
+        <v>20</v>
+      </c>
+      <c r="J103" s="1">
+        <v>54</v>
+      </c>
+      <c r="K103" s="1">
+        <v>0</v>
+      </c>
+      <c r="L103" s="1">
+        <v>0</v>
+      </c>
+      <c r="M103" s="1">
+        <v>0</v>
+      </c>
+      <c r="N103" s="1">
+        <v>0</v>
+      </c>
+      <c r="O103" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P103" s="1">
+        <v>23461</v>
+      </c>
+      <c r="Q103" s="1">
+        <v>8155</v>
+      </c>
+      <c r="R103" s="1">
+        <v>2.88</v>
+      </c>
+      <c r="S103" s="1">
+        <v>23424</v>
+      </c>
+    </row>
+    <row r="104" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>212</v>
+      </c>
+      <c r="B104" t="s">
+        <v>213</v>
+      </c>
+      <c r="C104" s="1">
+        <v>197</v>
+      </c>
+      <c r="D104" s="1">
+        <v>6</v>
+      </c>
+      <c r="E104" s="1">
+        <v>7</v>
+      </c>
+      <c r="F104" s="1">
+        <v>14</v>
+      </c>
+      <c r="G104" s="1">
+        <v>16</v>
+      </c>
+      <c r="H104" s="1">
+        <v>19</v>
+      </c>
+      <c r="I104" s="1">
+        <v>17</v>
+      </c>
+      <c r="J104" s="1">
+        <v>17</v>
+      </c>
+      <c r="K104" s="1">
+        <v>0</v>
+      </c>
+      <c r="L104" s="1">
+        <v>0</v>
+      </c>
+      <c r="M104" s="1">
+        <v>2</v>
+      </c>
+      <c r="N104" s="1">
+        <v>2</v>
+      </c>
+      <c r="O104" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="P104" s="1">
+        <v>25472</v>
+      </c>
+      <c r="Q104" s="1">
+        <v>6267</v>
+      </c>
+      <c r="R104" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="S104" s="1">
+        <v>8250</v>
+      </c>
+    </row>
+    <row r="105" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>216</v>
+      </c>
+      <c r="B105" t="s">
+        <v>217</v>
+      </c>
+      <c r="C105" s="1">
+        <v>59</v>
+      </c>
+      <c r="D105" s="1">
+        <v>3</v>
+      </c>
+      <c r="E105" s="1">
+        <v>4</v>
+      </c>
+      <c r="F105" s="1">
+        <v>16</v>
+      </c>
+      <c r="G105" s="1">
+        <v>26</v>
+      </c>
+      <c r="H105" s="1">
+        <v>13</v>
+      </c>
+      <c r="I105" s="1">
+        <v>9</v>
+      </c>
+      <c r="J105" s="1">
+        <v>26</v>
+      </c>
+      <c r="K105" s="1">
+        <v>0</v>
+      </c>
+      <c r="L105" s="1">
+        <v>0</v>
+      </c>
+      <c r="M105" s="1">
+        <v>0</v>
+      </c>
+      <c r="N105" s="1">
+        <v>2</v>
+      </c>
+      <c r="O105" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="P105" s="1">
+        <v>26900</v>
+      </c>
+      <c r="Q105" s="1">
+        <v>6436</v>
+      </c>
+      <c r="R105" s="1">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="S105" s="1">
+        <v>10333</v>
+      </c>
+    </row>
+    <row r="106" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>229</v>
+      </c>
+      <c r="B106" t="s">
+        <v>230</v>
+      </c>
+      <c r="C106" s="1">
+        <v>15</v>
+      </c>
+      <c r="D106" s="1">
+        <v>4</v>
+      </c>
+      <c r="E106" s="1">
+        <v>8</v>
+      </c>
+      <c r="F106" s="1">
+        <v>0</v>
+      </c>
+      <c r="G106" s="1">
+        <v>0</v>
+      </c>
+      <c r="H106" s="1">
+        <v>0</v>
+      </c>
+      <c r="I106" s="1">
+        <v>37</v>
+      </c>
+      <c r="J106" s="1">
+        <v>51</v>
+      </c>
+      <c r="K106" s="1">
+        <v>0</v>
+      </c>
+      <c r="L106" s="1">
+        <v>0</v>
+      </c>
+      <c r="M106" s="1">
+        <v>0</v>
+      </c>
+      <c r="N106" s="1">
+        <v>0</v>
+      </c>
+      <c r="O106" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P106" s="1">
+        <v>27687</v>
+      </c>
+      <c r="Q106" s="1">
+        <v>6266</v>
+      </c>
+      <c r="R106" s="1">
+        <v>3.47</v>
+      </c>
+      <c r="S106" s="1">
+        <v>14742</v>
+      </c>
+    </row>
+    <row r="107" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>223</v>
+      </c>
+      <c r="B107" t="s">
+        <v>224</v>
+      </c>
+      <c r="C107" s="1">
+        <v>43</v>
+      </c>
+      <c r="D107" s="1">
+        <v>2</v>
+      </c>
+      <c r="E107" s="1">
+        <v>6</v>
+      </c>
+      <c r="F107" s="1">
+        <v>5</v>
+      </c>
+      <c r="G107" s="1">
+        <v>16</v>
+      </c>
+      <c r="H107" s="1">
+        <v>33</v>
+      </c>
+      <c r="I107" s="1">
+        <v>12</v>
+      </c>
+      <c r="J107" s="1">
+        <v>0</v>
+      </c>
+      <c r="K107" s="1">
+        <v>22</v>
+      </c>
+      <c r="L107" s="1">
+        <v>0</v>
+      </c>
+      <c r="M107" s="1">
+        <v>0</v>
+      </c>
+      <c r="N107" s="1">
+        <v>3</v>
+      </c>
+      <c r="O107" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="P107" s="1">
+        <v>31966</v>
+      </c>
+      <c r="Q107" s="1">
+        <v>9814</v>
+      </c>
+      <c r="R107" s="1">
+        <v>1.26</v>
+      </c>
+      <c r="S107" s="1">
+        <v>13841</v>
+      </c>
+    </row>
+    <row r="108" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>231</v>
+      </c>
+      <c r="B108" t="s">
+        <v>232</v>
+      </c>
+      <c r="C108" s="1">
+        <v>15</v>
+      </c>
+      <c r="D108" s="1">
+        <v>0</v>
+      </c>
+      <c r="E108" s="1">
+        <v>2</v>
+      </c>
+      <c r="F108" s="1">
+        <v>4</v>
+      </c>
+      <c r="G108" s="1">
+        <v>6</v>
+      </c>
+      <c r="H108" s="1">
+        <v>13</v>
+      </c>
+      <c r="I108" s="1">
+        <v>27</v>
+      </c>
+      <c r="J108" s="1">
+        <v>38</v>
+      </c>
+      <c r="K108" s="1">
+        <v>0</v>
+      </c>
+      <c r="L108" s="1">
+        <v>0</v>
+      </c>
+      <c r="M108" s="1">
+        <v>10</v>
+      </c>
+      <c r="N108" s="1">
+        <v>0</v>
+      </c>
+      <c r="O108" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="P108" s="1">
+        <v>34713</v>
+      </c>
+      <c r="Q108" s="1">
+        <v>31200</v>
+      </c>
+      <c r="R108" s="1">
+        <v>1.73</v>
+      </c>
+      <c r="S108" s="1">
+        <v>82353</v>
+      </c>
+    </row>
+    <row r="109" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>233</v>
+      </c>
+      <c r="B109" t="s">
+        <v>234</v>
+      </c>
+      <c r="C109" s="1">
+        <v>21</v>
+      </c>
+      <c r="D109" s="1">
+        <v>0</v>
+      </c>
+      <c r="E109" s="1">
+        <v>0</v>
+      </c>
+      <c r="F109" s="1">
+        <v>1</v>
+      </c>
+      <c r="G109" s="1">
+        <v>9</v>
+      </c>
+      <c r="H109" s="1">
+        <v>18</v>
+      </c>
+      <c r="I109" s="1">
+        <v>19</v>
+      </c>
+      <c r="J109" s="1">
+        <v>36</v>
+      </c>
+      <c r="K109" s="1">
+        <v>12</v>
+      </c>
+      <c r="L109" s="1">
+        <v>0</v>
+      </c>
+      <c r="M109" s="1">
+        <v>5</v>
+      </c>
+      <c r="N109" s="1">
+        <v>0</v>
+      </c>
+      <c r="O109" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="P109" s="1">
+        <v>34857</v>
+      </c>
+      <c r="Q109" s="1">
+        <v>37172</v>
+      </c>
+      <c r="R109" s="1">
+        <v>1.44</v>
+      </c>
+      <c r="S109" s="1">
+        <v>55637</v>
+      </c>
+    </row>
+    <row r="110" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>225</v>
+      </c>
+      <c r="B110" t="s">
+        <v>226</v>
+      </c>
+      <c r="C110" s="1">
+        <v>6</v>
+      </c>
+      <c r="D110" s="1">
+        <v>0</v>
+      </c>
+      <c r="E110" s="1">
+        <v>3</v>
+      </c>
+      <c r="F110" s="1">
+        <v>33</v>
+      </c>
+      <c r="G110" s="1">
+        <v>0</v>
+      </c>
+      <c r="H110" s="1">
+        <v>35</v>
+      </c>
+      <c r="I110" s="1">
+        <v>0</v>
+      </c>
+      <c r="J110" s="1">
+        <v>0</v>
+      </c>
+      <c r="K110" s="1">
+        <v>0</v>
+      </c>
+      <c r="L110" s="1">
+        <v>0</v>
+      </c>
+      <c r="M110" s="1">
+        <v>29</v>
+      </c>
+      <c r="N110" s="1">
+        <v>0</v>
+      </c>
+      <c r="O110" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P110" s="1">
+        <v>34945</v>
+      </c>
+      <c r="Q110" s="1">
+        <v>23355</v>
+      </c>
+      <c r="R110" s="1">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="S110" s="1">
+        <v>57188</v>
+      </c>
+    </row>
+    <row r="111" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>235</v>
+      </c>
+      <c r="B111" t="s">
+        <v>236</v>
+      </c>
+      <c r="C111" s="1">
+        <v>9</v>
+      </c>
+      <c r="D111" s="1">
+        <v>0</v>
+      </c>
+      <c r="E111" s="1">
+        <v>0</v>
+      </c>
+      <c r="F111" s="1">
+        <v>2</v>
+      </c>
+      <c r="G111" s="1">
+        <v>0</v>
+      </c>
+      <c r="H111" s="1">
+        <v>11</v>
+      </c>
+      <c r="I111" s="1">
+        <v>37</v>
+      </c>
+      <c r="J111" s="1">
+        <v>0</v>
+      </c>
+      <c r="K111" s="1">
+        <v>45</v>
+      </c>
+      <c r="L111" s="1">
+        <v>0</v>
+      </c>
+      <c r="M111" s="1">
+        <v>5</v>
+      </c>
+      <c r="N111" s="1">
+        <v>0</v>
+      </c>
+      <c r="O111" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P111" s="1">
+        <v>41648</v>
+      </c>
+      <c r="Q111" s="1">
+        <v>49714</v>
+      </c>
+      <c r="R111" s="1">
+        <v>2.92</v>
+      </c>
+      <c r="S111" s="1">
+        <v>74746</v>
+      </c>
+    </row>
+    <row r="112" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>237</v>
+      </c>
+      <c r="B112" t="s">
+        <v>238</v>
+      </c>
+      <c r="C112" s="1">
+        <v>35</v>
+      </c>
+      <c r="D112" s="1">
+        <v>0</v>
+      </c>
+      <c r="E112" s="1">
+        <v>0</v>
+      </c>
+      <c r="F112" s="1">
+        <v>1</v>
+      </c>
+      <c r="G112" s="1">
+        <v>5</v>
+      </c>
+      <c r="H112" s="1">
+        <v>9</v>
+      </c>
+      <c r="I112" s="1">
+        <v>16</v>
+      </c>
+      <c r="J112" s="1">
+        <v>16</v>
+      </c>
+      <c r="K112" s="1">
+        <v>29</v>
+      </c>
+      <c r="L112" s="1">
+        <v>9</v>
+      </c>
+      <c r="M112" s="1">
+        <v>11</v>
+      </c>
+      <c r="N112" s="1">
+        <v>4</v>
+      </c>
+      <c r="O112" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="P112" s="1">
+        <v>59624</v>
+      </c>
+      <c r="Q112" s="1">
+        <v>69631</v>
+      </c>
+      <c r="R112" s="1">
+        <v>0.86</v>
+      </c>
+      <c r="S112" s="1">
+        <v>289127</v>
+      </c>
+    </row>
+    <row r="113" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>220</v>
+      </c>
+      <c r="B113" t="s">
+        <v>220</v>
+      </c>
+      <c r="C113" s="1">
+        <v>40</v>
+      </c>
+      <c r="D113" s="1">
+        <v>8</v>
+      </c>
+      <c r="E113" s="1">
+        <v>11</v>
+      </c>
+      <c r="F113" s="1">
+        <v>12</v>
+      </c>
+      <c r="G113" s="1">
+        <v>12</v>
+      </c>
+      <c r="H113" s="1">
+        <v>12</v>
+      </c>
+      <c r="I113" s="1">
+        <v>27</v>
+      </c>
+      <c r="J113" s="1">
+        <v>0</v>
+      </c>
+      <c r="K113" s="1">
+        <v>0</v>
+      </c>
+      <c r="L113" s="1">
+        <v>0</v>
+      </c>
+      <c r="M113" s="1">
+        <v>10</v>
+      </c>
+      <c r="N113" s="1">
+        <v>6</v>
+      </c>
+      <c r="O113" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="P113" s="1">
+        <v>69890</v>
+      </c>
+      <c r="Q113" s="1">
+        <v>18081</v>
+      </c>
+      <c r="R113" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="S113" s="1">
+        <v>7948</v>
+      </c>
+    </row>
+    <row r="114" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>239</v>
+      </c>
+      <c r="B114" t="s">
+        <v>240</v>
+      </c>
+      <c r="C114" s="1">
+        <v>30</v>
+      </c>
+      <c r="D114" s="1">
+        <v>0</v>
+      </c>
+      <c r="E114" s="1">
+        <v>0</v>
+      </c>
+      <c r="F114" s="1">
+        <v>0</v>
+      </c>
+      <c r="G114" s="1">
+        <v>0</v>
+      </c>
+      <c r="H114" s="1">
+        <v>0</v>
+      </c>
+      <c r="I114" s="1">
+        <v>24</v>
+      </c>
+      <c r="J114" s="1">
+        <v>0</v>
+      </c>
+      <c r="K114" s="1">
+        <v>22</v>
+      </c>
+      <c r="L114" s="1">
+        <v>13</v>
+      </c>
+      <c r="M114" s="1">
+        <v>25</v>
+      </c>
+      <c r="N114" s="1">
+        <v>16</v>
+      </c>
+      <c r="O114" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="P114" s="1">
+        <v>150361</v>
+      </c>
+      <c r="Q114" s="1">
+        <v>287955</v>
+      </c>
+      <c r="R114" s="1">
+        <v>1.31</v>
+      </c>
+      <c r="S114" s="1">
+        <v>461073</v>
+      </c>
+    </row>
+    <row r="115" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>241</v>
+      </c>
+      <c r="B115" t="s">
+        <v>242</v>
+      </c>
+      <c r="C115" s="1">
+        <v>21</v>
+      </c>
+      <c r="D115" s="1">
+        <v>0</v>
+      </c>
+      <c r="E115" s="1">
+        <v>0</v>
+      </c>
+      <c r="F115" s="1">
+        <v>0</v>
+      </c>
+      <c r="G115" s="1">
+        <v>0</v>
+      </c>
+      <c r="H115" s="1">
+        <v>0</v>
+      </c>
+      <c r="I115" s="1">
+        <v>0</v>
+      </c>
+      <c r="J115" s="1">
+        <v>0</v>
+      </c>
+      <c r="K115" s="1">
+        <v>0</v>
+      </c>
+      <c r="L115" s="1">
+        <v>0</v>
+      </c>
+      <c r="M115" s="1">
+        <v>65</v>
+      </c>
+      <c r="N115" s="1">
+        <v>35</v>
+      </c>
+      <c r="O115" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P115" s="1">
+        <v>309521</v>
+      </c>
+      <c r="Q115" s="1">
+        <v>324899</v>
+      </c>
+      <c r="R115" s="1">
+        <v>4.97</v>
+      </c>
+      <c r="S115" s="1">
+        <v>552806</v>
+      </c>
+    </row>
+    <row r="116" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>243</v>
+      </c>
+      <c r="B116" t="s">
+        <v>244</v>
+      </c>
+      <c r="C116" s="1">
+        <v>7</v>
+      </c>
+      <c r="D116" s="1">
+        <v>0</v>
+      </c>
+      <c r="E116" s="1">
+        <v>0</v>
+      </c>
+      <c r="F116" s="1">
+        <v>0</v>
+      </c>
+      <c r="G116" s="1">
+        <v>0</v>
+      </c>
+      <c r="H116" s="1">
+        <v>0</v>
+      </c>
+      <c r="I116" s="1">
+        <v>0</v>
+      </c>
+      <c r="J116" s="1">
+        <v>0</v>
+      </c>
+      <c r="K116" s="1">
+        <v>0</v>
+      </c>
+      <c r="L116" s="1">
+        <v>0</v>
+      </c>
+      <c r="M116" s="1">
+        <v>0</v>
+      </c>
+      <c r="N116" s="1">
+        <v>100</v>
+      </c>
+      <c r="O116" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P116" s="1">
+        <v>519319</v>
+      </c>
+      <c r="Q116" s="1">
+        <v>532986</v>
+      </c>
+      <c r="R116" s="1">
+        <v>10</v>
+      </c>
+      <c r="S116" s="1">
+        <v>662782</v>
+      </c>
+    </row>
+    <row r="117" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>245</v>
+      </c>
+      <c r="B117" t="s">
+        <v>246</v>
+      </c>
+      <c r="C117" s="1">
+        <v>15</v>
+      </c>
+      <c r="D117" s="1">
+        <v>0</v>
+      </c>
+      <c r="E117" s="1">
+        <v>0</v>
+      </c>
+      <c r="F117" s="1">
+        <v>0</v>
+      </c>
+      <c r="G117" s="1">
+        <v>0</v>
+      </c>
+      <c r="H117" s="1">
+        <v>0</v>
+      </c>
+      <c r="I117" s="1">
+        <v>0</v>
+      </c>
+      <c r="J117" s="1">
+        <v>0</v>
+      </c>
+      <c r="K117" s="1">
+        <v>0</v>
+      </c>
+      <c r="L117" s="1">
+        <v>0</v>
+      </c>
+      <c r="M117" s="1">
+        <v>0</v>
+      </c>
+      <c r="N117" s="1">
+        <v>100</v>
+      </c>
+      <c r="O117" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P117" s="1">
+        <v>535709</v>
+      </c>
+      <c r="Q117" s="1">
+        <v>536212</v>
+      </c>
+      <c r="R117" s="1">
+        <v>10</v>
+      </c>
+      <c r="S117" s="1">
+        <v>622951</v>
+      </c>
+    </row>
+    <row r="118" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>247</v>
+      </c>
+      <c r="B118" t="s">
+        <v>248</v>
+      </c>
+      <c r="C118" s="1">
+        <v>19</v>
+      </c>
+      <c r="D118" s="1">
+        <v>0</v>
+      </c>
+      <c r="E118" s="1">
+        <v>0</v>
+      </c>
+      <c r="F118" s="1">
+        <v>0</v>
+      </c>
+      <c r="G118" s="1">
+        <v>0</v>
+      </c>
+      <c r="H118" s="1">
+        <v>0</v>
+      </c>
+      <c r="I118" s="1">
+        <v>0</v>
+      </c>
+      <c r="J118" s="1">
+        <v>0</v>
+      </c>
+      <c r="K118" s="1">
+        <v>0</v>
+      </c>
+      <c r="L118" s="1">
+        <v>0</v>
+      </c>
+      <c r="M118" s="1">
+        <v>0</v>
+      </c>
+      <c r="N118" s="1">
+        <v>100</v>
+      </c>
+      <c r="O118" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P118" s="1">
+        <v>553859</v>
+      </c>
+      <c r="Q118" s="1">
+        <v>552176</v>
+      </c>
+      <c r="R118" s="1">
+        <v>10</v>
+      </c>
+      <c r="S118" s="1">
+        <v>649036</v>
+      </c>
+    </row>
+    <row r="119" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="C119" s="1"/>
+      <c r="D119" s="1"/>
+      <c r="E119" s="1"/>
+      <c r="F119" s="1"/>
+      <c r="G119" s="1"/>
+      <c r="H119" s="1"/>
+      <c r="I119" s="1"/>
+      <c r="J119" s="1"/>
+      <c r="K119" s="1"/>
+      <c r="L119" s="1"/>
+      <c r="M119" s="1"/>
+      <c r="N119" s="1"/>
+    </row>
+    <row r="120" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>249</v>
+      </c>
+      <c r="B120" t="s">
+        <v>250</v>
+      </c>
+      <c r="C120" s="1">
+        <v>78</v>
+      </c>
+      <c r="D120" s="1">
+        <v>3</v>
+      </c>
+      <c r="E120" s="1">
+        <v>6</v>
+      </c>
+      <c r="F120" s="1">
+        <v>12</v>
+      </c>
+      <c r="G120" s="1">
+        <v>14</v>
+      </c>
+      <c r="H120" s="1">
+        <v>21</v>
+      </c>
+      <c r="I120" s="1">
+        <v>15</v>
+      </c>
+      <c r="J120" s="1">
+        <v>10</v>
+      </c>
+      <c r="K120" s="1">
+        <v>14</v>
+      </c>
+      <c r="L120" s="1">
+        <v>0</v>
+      </c>
+      <c r="M120" s="1">
+        <v>3</v>
+      </c>
+      <c r="N120" s="1">
+        <v>2</v>
+      </c>
+      <c r="O120" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="P120" s="1">
+        <v>26310</v>
+      </c>
+      <c r="Q120" s="1">
+        <v>15150</v>
+      </c>
+      <c r="R120" s="1">
+        <v>0.49</v>
+      </c>
+      <c r="S120" s="1">
+        <v>13993</v>
+      </c>
+    </row>
+    <row r="121" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>252</v>
+      </c>
+      <c r="B121" t="s">
+        <v>253</v>
+      </c>
+      <c r="C121" s="1">
+        <v>143</v>
+      </c>
+      <c r="D121" s="1">
+        <v>1</v>
+      </c>
+      <c r="E121" s="1">
+        <v>3</v>
+      </c>
+      <c r="F121" s="1">
+        <v>6</v>
+      </c>
+      <c r="G121" s="1">
+        <v>10</v>
+      </c>
+      <c r="H121" s="1">
+        <v>15</v>
+      </c>
+      <c r="I121" s="1">
+        <v>14</v>
+      </c>
+      <c r="J121" s="1">
+        <v>10</v>
+      </c>
+      <c r="K121" s="1">
+        <v>22</v>
+      </c>
+      <c r="L121" s="1">
+        <v>10</v>
+      </c>
+      <c r="M121" s="1">
+        <v>5</v>
+      </c>
+      <c r="N121" s="1">
+        <v>2</v>
+      </c>
+      <c r="O121" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="P121" s="1">
+        <v>43547</v>
+      </c>
+      <c r="Q121" s="1">
+        <v>29399</v>
+      </c>
+      <c r="R121" s="1">
+        <v>0.43</v>
+      </c>
+      <c r="S121" s="1">
+        <v>49544</v>
+      </c>
+    </row>
+    <row r="122" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>254</v>
+      </c>
+      <c r="B122" t="s">
+        <v>254</v>
+      </c>
+      <c r="C122" s="1">
+        <v>79</v>
+      </c>
+      <c r="D122" s="1">
+        <v>5</v>
+      </c>
+      <c r="E122" s="1">
+        <v>7</v>
+      </c>
+      <c r="F122" s="1">
+        <v>4</v>
+      </c>
+      <c r="G122" s="1">
+        <v>17</v>
+      </c>
+      <c r="H122" s="1">
+        <v>0</v>
+      </c>
+      <c r="I122" s="1">
+        <v>10</v>
+      </c>
+      <c r="J122" s="1">
+        <v>13</v>
+      </c>
+      <c r="K122" s="1">
+        <v>17</v>
+      </c>
+      <c r="L122" s="1">
+        <v>0</v>
+      </c>
+      <c r="M122" s="1">
+        <v>14</v>
+      </c>
+      <c r="N122" s="1">
+        <v>11</v>
+      </c>
+      <c r="O122" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="P122" s="1">
+        <v>99268</v>
+      </c>
+      <c r="Q122" s="1">
+        <v>36705</v>
+      </c>
+      <c r="R122" s="1">
+        <v>0.43</v>
+      </c>
+      <c r="S122" s="1">
+        <v>120739</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A120:S122">
+    <sortCondition ref="P120:P122"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52DF63B5-288D-4CBE-AF14-28FA1500C1F7}">
+  <dimension ref="A1:S124"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="29.85546875" customWidth="1"/>
+    <col min="2" max="2" width="31.28515625" customWidth="1"/>
+    <col min="4" max="14" width="12.28515625" customWidth="1"/>
+    <col min="15" max="19" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="8"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="8">
+        <v>798</v>
+      </c>
+      <c r="E4" s="8">
+        <v>266</v>
+      </c>
+      <c r="F4" s="8">
+        <v>76</v>
+      </c>
+      <c r="G4" s="8">
+        <v>24</v>
+      </c>
+      <c r="H4" s="8">
+        <v>24</v>
+      </c>
+      <c r="I4" s="8">
+        <v>11</v>
+      </c>
+      <c r="J4" s="8">
+        <v>8</v>
+      </c>
+      <c r="K4" s="8">
+        <v>6</v>
+      </c>
+      <c r="L4" s="8">
+        <v>5</v>
+      </c>
+      <c r="M4" s="8">
+        <v>29</v>
+      </c>
+      <c r="N4" s="8">
+        <v>48</v>
+      </c>
+      <c r="O4" s="9"/>
+      <c r="P4" s="9"/>
+      <c r="Q4" s="9"/>
+      <c r="R4" s="9"/>
+      <c r="S4" s="9"/>
+    </row>
+    <row r="5" spans="1:19" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="2"/>
       <c r="C5" s="10" t="s">
@@ -1912,7 +8905,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:19" s="1" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:19" s="1" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>2</v>
       </c>
@@ -1971,7 +8964,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:19" s="1" customFormat="1" ht="57" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:19" s="1" customFormat="1" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
       <c r="B7" s="2"/>
       <c r="C7" s="10" t="s">
@@ -1989,7 +8982,7 @@
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -2048,7 +9041,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -2107,7 +9100,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -2166,7 +9159,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -2225,7 +9218,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>30</v>
       </c>
@@ -2284,7 +9277,7 @@
         <v>1117</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -2343,7 +9336,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>34</v>
       </c>
@@ -2402,7 +9395,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>36</v>
       </c>
@@ -2461,7 +9454,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -2520,7 +9513,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -2579,7 +9572,7 @@
         <v>1274</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -2638,7 +9631,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>44</v>
       </c>
@@ -2697,7 +9690,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>46</v>
       </c>
@@ -2756,7 +9749,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>48</v>
       </c>
@@ -2815,7 +9808,7 @@
         <v>1280</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>50</v>
       </c>
@@ -2874,7 +9867,7 @@
         <v>1071</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>52</v>
       </c>
@@ -2933,7 +9926,7 @@
         <v>1502</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>54</v>
       </c>
@@ -2992,7 +9985,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>56</v>
       </c>
@@ -3051,7 +10044,7 @@
         <v>1595</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>58</v>
       </c>
@@ -3110,7 +10103,7 @@
         <v>1418</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>62</v>
       </c>
@@ -3169,7 +10162,7 @@
         <v>1397</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>60</v>
       </c>
@@ -3228,7 +10221,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>64</v>
       </c>
@@ -3287,7 +10280,7 @@
         <v>1431</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>66</v>
       </c>
@@ -3346,7 +10339,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>68</v>
       </c>
@@ -3405,7 +10398,7 @@
         <v>1501</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>70</v>
       </c>
@@ -3464,7 +10457,7 @@
         <v>1398</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>72</v>
       </c>
@@ -3523,7 +10516,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>74</v>
       </c>
@@ -3582,7 +10575,7 @@
         <v>1662</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>78</v>
       </c>
@@ -3641,7 +10634,7 @@
         <v>1683</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>76</v>
       </c>
@@ -3700,7 +10693,7 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>84</v>
       </c>
@@ -3759,7 +10752,7 @@
         <v>1824</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>86</v>
       </c>
@@ -3818,7 +10811,7 @@
         <v>1977</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>82</v>
       </c>
@@ -3877,7 +10870,7 @@
         <v>2254</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>80</v>
       </c>
@@ -3936,7 +10929,7 @@
         <v>1388</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>90</v>
       </c>
@@ -3995,7 +10988,7 @@
         <v>1946</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>94</v>
       </c>
@@ -4054,7 +11047,7 @@
         <v>2392</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>96</v>
       </c>
@@ -4113,7 +11106,7 @@
         <v>2038</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>92</v>
       </c>
@@ -4172,7 +11165,7 @@
         <v>1915</v>
       </c>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>88</v>
       </c>
@@ -4231,7 +11224,7 @@
         <v>1382</v>
       </c>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>98</v>
       </c>
@@ -4290,7 +11283,7 @@
         <v>1931</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>106</v>
       </c>
@@ -4349,7 +11342,7 @@
         <v>2285</v>
       </c>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>108</v>
       </c>
@@ -4408,7 +11401,7 @@
         <v>2337</v>
       </c>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>102</v>
       </c>
@@ -4467,7 +11460,7 @@
         <v>1907</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>104</v>
       </c>
@@ -4526,7 +11519,7 @@
         <v>1687</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>100</v>
       </c>
@@ -4585,7 +11578,7 @@
         <v>2301</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>110</v>
       </c>
@@ -4644,7 +11637,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>112</v>
       </c>
@@ -4703,7 +11696,7 @@
         <v>1849</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>114</v>
       </c>
@@ -4762,7 +11755,7 @@
         <v>2059</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>120</v>
       </c>
@@ -4821,7 +11814,7 @@
         <v>2757</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>122</v>
       </c>
@@ -4880,7 +11873,7 @@
         <v>2272</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>116</v>
       </c>
@@ -4939,7 +11932,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>118</v>
       </c>
@@ -4998,7 +11991,7 @@
         <v>2338</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>128</v>
       </c>
@@ -5057,7 +12050,7 @@
         <v>2959</v>
       </c>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>134</v>
       </c>
@@ -5116,7 +12109,7 @@
         <v>3336</v>
       </c>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>132</v>
       </c>
@@ -5175,7 +12168,7 @@
         <v>2688</v>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>141</v>
       </c>
@@ -5234,7 +12227,7 @@
         <v>3345</v>
       </c>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>143</v>
       </c>
@@ -5293,7 +12286,7 @@
         <v>3554</v>
       </c>
     </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>149</v>
       </c>
@@ -5352,7 +12345,7 @@
         <v>3490</v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>147</v>
       </c>
@@ -5411,7 +12404,7 @@
         <v>3503</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>136</v>
       </c>
@@ -5470,7 +12463,7 @@
         <v>2534</v>
       </c>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>139</v>
       </c>
@@ -5529,7 +12522,7 @@
         <v>3674</v>
       </c>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>124</v>
       </c>
@@ -5588,7 +12581,7 @@
         <v>1436</v>
       </c>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>126</v>
       </c>
@@ -5647,7 +12640,7 @@
         <v>1351</v>
       </c>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>130</v>
       </c>
@@ -5706,7 +12699,7 @@
         <v>1239</v>
       </c>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>157</v>
       </c>
@@ -5765,7 +12758,7 @@
         <v>3520</v>
       </c>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>151</v>
       </c>
@@ -5824,7 +12817,7 @@
         <v>2094</v>
       </c>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>155</v>
       </c>
@@ -5883,7 +12876,7 @@
         <v>1864</v>
       </c>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>145</v>
       </c>
@@ -5942,7 +12935,7 @@
         <v>2153</v>
       </c>
     </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>159</v>
       </c>
@@ -6001,7 +12994,7 @@
         <v>1712</v>
       </c>
     </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>153</v>
       </c>
@@ -6060,7 +13053,7 @@
         <v>2303</v>
       </c>
     </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>167</v>
       </c>
@@ -6119,7 +13112,7 @@
         <v>2370</v>
       </c>
     </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>171</v>
       </c>
@@ -6178,7 +13171,7 @@
         <v>2562</v>
       </c>
     </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>163</v>
       </c>
@@ -6237,7 +13230,7 @@
         <v>2952</v>
       </c>
     </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>161</v>
       </c>
@@ -6296,7 +13289,7 @@
         <v>2234</v>
       </c>
     </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>178</v>
       </c>
@@ -6355,7 +13348,7 @@
         <v>4506</v>
       </c>
     </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>165</v>
       </c>
@@ -6414,7 +13407,7 @@
         <v>2509</v>
       </c>
     </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>173</v>
       </c>
@@ -6473,7 +13466,7 @@
         <v>3530</v>
       </c>
     </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>184</v>
       </c>
@@ -6532,7 +13525,7 @@
         <v>5277</v>
       </c>
     </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>188</v>
       </c>
@@ -6591,7 +13584,7 @@
         <v>5479</v>
       </c>
     </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>169</v>
       </c>
@@ -6650,7 +13643,7 @@
         <v>3394</v>
       </c>
     </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>182</v>
       </c>
@@ -6709,7 +13702,7 @@
         <v>3660</v>
       </c>
     </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>192</v>
       </c>
@@ -6768,7 +13761,7 @@
         <v>2564</v>
       </c>
     </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>175</v>
       </c>
@@ -6827,7 +13820,7 @@
         <v>2266</v>
       </c>
     </row>
-    <row r="90" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>186</v>
       </c>
@@ -6886,7 +13879,7 @@
         <v>3060</v>
       </c>
     </row>
-    <row r="91" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>180</v>
       </c>
@@ -6945,7 +13938,7 @@
         <v>2038</v>
       </c>
     </row>
-    <row r="92" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>194</v>
       </c>
@@ -7004,7 +13997,7 @@
         <v>3496</v>
       </c>
     </row>
-    <row r="93" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>196</v>
       </c>
@@ -7063,7 +14056,7 @@
         <v>8141</v>
       </c>
     </row>
-    <row r="94" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>202</v>
       </c>
@@ -7122,7 +14115,7 @@
         <v>12214</v>
       </c>
     </row>
-    <row r="95" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>198</v>
       </c>
@@ -7181,7 +14174,7 @@
         <v>4048</v>
       </c>
     </row>
-    <row r="96" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>206</v>
       </c>
@@ -7240,7 +14233,7 @@
         <v>7453</v>
       </c>
     </row>
-    <row r="97" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>208</v>
       </c>
@@ -7299,7 +14292,7 @@
         <v>4961</v>
       </c>
     </row>
-    <row r="98" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>200</v>
       </c>
@@ -7358,7 +14351,7 @@
         <v>3034</v>
       </c>
     </row>
-    <row r="99" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>190</v>
       </c>
@@ -7417,7 +14410,7 @@
         <v>2957</v>
       </c>
     </row>
-    <row r="100" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>204</v>
       </c>
@@ -7476,7 +14469,7 @@
         <v>3577</v>
       </c>
     </row>
-    <row r="101" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>210</v>
       </c>
@@ -7535,7 +14528,7 @@
         <v>3604</v>
       </c>
     </row>
-    <row r="102" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>218</v>
       </c>
@@ -7594,7 +14587,7 @@
         <v>9592</v>
       </c>
     </row>
-    <row r="103" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>214</v>
       </c>
@@ -7653,7 +14646,7 @@
         <v>10212</v>
       </c>
     </row>
-    <row r="104" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>221</v>
       </c>
@@ -7712,7 +14705,7 @@
         <v>7695</v>
       </c>
     </row>
-    <row r="105" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>227</v>
       </c>
@@ -7771,7 +14764,7 @@
         <v>23424</v>
       </c>
     </row>
-    <row r="106" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>212</v>
       </c>
@@ -7830,7 +14823,7 @@
         <v>8250</v>
       </c>
     </row>
-    <row r="107" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>216</v>
       </c>
@@ -7889,7 +14882,7 @@
         <v>10333</v>
       </c>
     </row>
-    <row r="108" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>229</v>
       </c>
@@ -7948,7 +14941,7 @@
         <v>14742</v>
       </c>
     </row>
-    <row r="109" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>223</v>
       </c>
@@ -8007,7 +15000,7 @@
         <v>13841</v>
       </c>
     </row>
-    <row r="110" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>231</v>
       </c>
@@ -8066,7 +15059,7 @@
         <v>82353</v>
       </c>
     </row>
-    <row r="111" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>233</v>
       </c>
@@ -8125,7 +15118,7 @@
         <v>55637</v>
       </c>
     </row>
-    <row r="112" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>225</v>
       </c>
@@ -8184,7 +15177,7 @@
         <v>57188</v>
       </c>
     </row>
-    <row r="113" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>235</v>
       </c>
@@ -8243,7 +15236,7 @@
         <v>74746</v>
       </c>
     </row>
-    <row r="114" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>237</v>
       </c>
@@ -8302,7 +15295,7 @@
         <v>289127</v>
       </c>
     </row>
-    <row r="115" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>220</v>
       </c>
@@ -8361,7 +15354,7 @@
         <v>7948</v>
       </c>
     </row>
-    <row r="116" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>239</v>
       </c>
@@ -8420,7 +15413,7 @@
         <v>461073</v>
       </c>
     </row>
-    <row r="117" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>241</v>
       </c>
@@ -8479,7 +15472,7 @@
         <v>552806</v>
       </c>
     </row>
-    <row r="118" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>243</v>
       </c>
@@ -8538,7 +15531,7 @@
         <v>662782</v>
       </c>
     </row>
-    <row r="119" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>245</v>
       </c>
@@ -8597,7 +15590,7 @@
         <v>622951</v>
       </c>
     </row>
-    <row r="120" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>247</v>
       </c>
@@ -8656,7 +15649,7 @@
         <v>649036</v>
       </c>
     </row>
-    <row r="121" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:19" x14ac:dyDescent="0.25">
       <c r="C121" s="1"/>
       <c r="D121" s="1"/>
       <c r="E121" s="1"/>
@@ -8670,7 +15663,7 @@
       <c r="M121" s="1"/>
       <c r="N121" s="1"/>
     </row>
-    <row r="122" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>249</v>
       </c>
@@ -8729,7 +15722,7 @@
         <v>13993</v>
       </c>
     </row>
-    <row r="123" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>252</v>
       </c>
@@ -8788,7 +15781,7 @@
         <v>49544</v>
       </c>
     </row>
-    <row r="124" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>254</v>
       </c>
@@ -8848,9 +15841,6 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A122:S124">
-    <sortCondition ref="P122:P124"/>
-  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>